--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South America Copa Libertadores_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South America Copa Libertadores_2025.xlsx
@@ -926,10 +926,10 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW2" t="n">
         <v>10</v>
@@ -938,10 +938,10 @@
         <v>12</v>
       </c>
       <c r="AY2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
         <v>7</v>
@@ -1144,10 +1144,10 @@
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW3" t="n">
         <v>9</v>
@@ -1156,10 +1156,10 @@
         <v>13</v>
       </c>
       <c r="AY3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA3" t="n">
         <v>4</v>
@@ -1362,10 +1362,10 @@
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW4" t="n">
         <v>8</v>
@@ -1374,10 +1374,10 @@
         <v>7</v>
       </c>
       <c r="AY4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA4" t="n">
         <v>4</v>
@@ -1571,19 +1571,19 @@
         <v>1.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.73</v>
+        <v>3.47</v>
       </c>
       <c r="AU5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW5" t="n">
         <v>13</v>
@@ -1592,10 +1592,10 @@
         <v>5</v>
       </c>
       <c r="AY5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA5" t="n">
         <v>5</v>
@@ -1789,19 +1789,19 @@
         <v>0.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.63</v>
+        <v>3.37</v>
       </c>
       <c r="AU6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW6" t="n">
         <v>12</v>
@@ -1810,10 +1810,10 @@
         <v>12</v>
       </c>
       <c r="AY6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA6" t="n">
         <v>5</v>
@@ -2007,19 +2007,19 @@
         <v>1.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.42</v>
+        <v>3.16</v>
       </c>
       <c r="AU7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW7" t="n">
         <v>23</v>
@@ -2028,10 +2028,10 @@
         <v>3</v>
       </c>
       <c r="AY7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA7" t="n">
         <v>5</v>
@@ -2234,10 +2234,10 @@
         <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW8" t="n">
         <v>14</v>
@@ -2246,10 +2246,10 @@
         <v>8</v>
       </c>
       <c r="AY8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
         <v>3</v>
@@ -2452,10 +2452,10 @@
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW9" t="n">
         <v>9</v>
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="AY9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA9" t="n">
         <v>9</v>
@@ -2661,19 +2661,19 @@
         <v>1.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="AU10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW10" t="n">
         <v>8</v>
@@ -2682,10 +2682,10 @@
         <v>7</v>
       </c>
       <c r="AY10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA10" t="n">
         <v>3</v>
@@ -2888,7 +2888,7 @@
         <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -2897,13 +2897,13 @@
         <v>7</v>
       </c>
       <c r="AX11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA11" t="n">
         <v>9</v>
@@ -3106,10 +3106,10 @@
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW12" t="n">
         <v>9</v>
@@ -3118,10 +3118,10 @@
         <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA12" t="n">
         <v>4</v>
@@ -3315,31 +3315,31 @@
         <v>1.1</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AS13" t="n">
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AU13" t="n">
         <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX13" t="n">
         <v>9</v>
       </c>
       <c r="AY13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA13" t="n">
         <v>6</v>
@@ -3533,31 +3533,31 @@
         <v>1.9</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AS14" t="n">
         <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AU14" t="n">
         <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX14" t="n">
         <v>8</v>
       </c>
       <c r="AY14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA14" t="n">
         <v>2</v>
@@ -3760,10 +3760,10 @@
         <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW15" t="n">
         <v>12</v>
@@ -3772,10 +3772,10 @@
         <v>5</v>
       </c>
       <c r="AY15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA15" t="n">
         <v>2</v>
@@ -3969,19 +3969,19 @@
         <v>1</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.63</v>
+        <v>3.36</v>
       </c>
       <c r="AU16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW16" t="n">
         <v>21</v>
@@ -3990,10 +3990,10 @@
         <v>5</v>
       </c>
       <c r="AY16" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AZ16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA16" t="n">
         <v>5</v>
@@ -4187,16 +4187,16 @@
         <v>0.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AT17" t="n">
-        <v>4.08</v>
+        <v>3.82</v>
       </c>
       <c r="AU17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -4205,13 +4205,13 @@
         <v>15</v>
       </c>
       <c r="AX17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA17" t="n">
         <v>5</v>
@@ -4405,19 +4405,19 @@
         <v>1.33</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.14</v>
+        <v>2.87</v>
       </c>
       <c r="AU18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW18" t="n">
         <v>14</v>
@@ -4426,10 +4426,10 @@
         <v>3</v>
       </c>
       <c r="AY18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA18" t="n">
         <v>12</v>
@@ -4623,19 +4623,19 @@
         <v>1.25</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="AU19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW19" t="n">
         <v>12</v>
@@ -4644,10 +4644,10 @@
         <v>10</v>
       </c>
       <c r="AY19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA19" t="n">
         <v>1</v>
@@ -4841,19 +4841,19 @@
         <v>0.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.01</v>
+        <v>2.75</v>
       </c>
       <c r="AU20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW20" t="n">
         <v>17</v>
@@ -4862,10 +4862,10 @@
         <v>2</v>
       </c>
       <c r="AY20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA20" t="n">
         <v>9</v>
@@ -5059,19 +5059,19 @@
         <v>1</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.93</v>
+        <v>2.69</v>
       </c>
       <c r="AU21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW21" t="n">
         <v>9</v>
@@ -5080,10 +5080,10 @@
         <v>8</v>
       </c>
       <c r="AY21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA21" t="n">
         <v>3</v>
@@ -5277,19 +5277,19 @@
         <v>1.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.55</v>
+        <v>3.32</v>
       </c>
       <c r="AU22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW22" t="n">
         <v>15</v>
@@ -5298,10 +5298,10 @@
         <v>5</v>
       </c>
       <c r="AY22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA22" t="n">
         <v>5</v>
@@ -5495,19 +5495,19 @@
         <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.03</v>
+        <v>0.89</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="AU23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW23" t="n">
         <v>7</v>
@@ -5516,10 +5516,10 @@
         <v>11</v>
       </c>
       <c r="AY23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA23" t="n">
         <v>7</v>
@@ -5713,19 +5713,19 @@
         <v>1.33</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.03</v>
+        <v>2.77</v>
       </c>
       <c r="AU24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW24" t="n">
         <v>11</v>
@@ -5734,10 +5734,10 @@
         <v>11</v>
       </c>
       <c r="AY24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA24" t="n">
         <v>3</v>
@@ -5931,19 +5931,19 @@
         <v>1.9</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.04</v>
+        <v>0.91</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.37</v>
+        <v>2.24</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.41</v>
+        <v>3.15</v>
       </c>
       <c r="AU25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW25" t="n">
         <v>12</v>
@@ -5952,10 +5952,10 @@
         <v>6</v>
       </c>
       <c r="AY25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA25" t="n">
         <v>10</v>
@@ -6149,19 +6149,19 @@
         <v>1.75</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AT26" t="n">
-        <v>3.49</v>
+        <v>3.23</v>
       </c>
       <c r="AU26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW26" t="n">
         <v>13</v>
@@ -6170,10 +6170,10 @@
         <v>5</v>
       </c>
       <c r="AY26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA26" t="n">
         <v>11</v>
@@ -6367,19 +6367,19 @@
         <v>1.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="AT27" t="n">
-        <v>3.89</v>
+        <v>3.61</v>
       </c>
       <c r="AU27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW27" t="n">
         <v>0</v>
@@ -6388,10 +6388,10 @@
         <v>4</v>
       </c>
       <c r="AY27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA27" t="n">
         <v>1</v>
@@ -6585,19 +6585,19 @@
         <v>1</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AT28" t="n">
-        <v>3.17</v>
+        <v>2.91</v>
       </c>
       <c r="AU28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW28" t="n">
         <v>7</v>
@@ -6606,10 +6606,10 @@
         <v>6</v>
       </c>
       <c r="AY28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA28" t="n">
         <v>5</v>
@@ -6803,13 +6803,13 @@
         <v>1.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.32</v>
+        <v>3.06</v>
       </c>
       <c r="AU29" t="n">
         <v>-1</v>
@@ -7021,19 +7021,19 @@
         <v>1.1</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.17</v>
+        <v>2.91</v>
       </c>
       <c r="AU30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW30" t="n">
         <v>19</v>
@@ -7042,10 +7042,10 @@
         <v>3</v>
       </c>
       <c r="AY30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA30" t="n">
         <v>13</v>
@@ -7239,16 +7239,16 @@
         <v>1.25</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.06</v>
+        <v>2.8</v>
       </c>
       <c r="AU31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV31" t="n">
         <v>0</v>
@@ -7257,13 +7257,13 @@
         <v>17</v>
       </c>
       <c r="AX31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA31" t="n">
         <v>6</v>
@@ -7466,10 +7466,10 @@
         <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW32" t="n">
         <v>3</v>
@@ -7478,10 +7478,10 @@
         <v>7</v>
       </c>
       <c r="AY32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ32" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA32" t="n">
         <v>4</v>
@@ -7675,19 +7675,19 @@
         <v>1</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AS33" t="n">
         <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AU33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW33" t="n">
         <v>13</v>
@@ -7696,10 +7696,10 @@
         <v>5</v>
       </c>
       <c r="AY33" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ33" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA33" t="n">
         <v>6</v>
@@ -7902,10 +7902,10 @@
         <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV34" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW34" t="n">
         <v>10</v>
@@ -7914,10 +7914,10 @@
         <v>12</v>
       </c>
       <c r="AY34" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ34" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA34" t="n">
         <v>3</v>
@@ -8120,10 +8120,10 @@
         <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW35" t="n">
         <v>5</v>
@@ -8132,10 +8132,10 @@
         <v>3</v>
       </c>
       <c r="AY35" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA35" t="n">
         <v>1</v>
@@ -8329,19 +8329,19 @@
         <v>1.5</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AS36" t="n">
         <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AU36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW36" t="n">
         <v>14</v>
@@ -8350,10 +8350,10 @@
         <v>5</v>
       </c>
       <c r="AY36" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ36" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA36" t="n">
         <v>5</v>
@@ -8547,19 +8547,19 @@
         <v>1.33</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AS37" t="n">
         <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AU37" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW37" t="n">
         <v>8</v>
@@ -8568,10 +8568,10 @@
         <v>8</v>
       </c>
       <c r="AY37" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ37" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA37" t="n">
         <v>5</v>
@@ -8774,10 +8774,10 @@
         <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW38" t="n">
         <v>12</v>
@@ -8786,10 +8786,10 @@
         <v>3</v>
       </c>
       <c r="AY38" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA38" t="n">
         <v>8</v>
@@ -8992,10 +8992,10 @@
         <v>0</v>
       </c>
       <c r="AU39" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV39" t="n">
         <v>7</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>8</v>
       </c>
       <c r="AW39" t="n">
         <v>8</v>
@@ -9004,10 +9004,10 @@
         <v>10</v>
       </c>
       <c r="AY39" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ39" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA39" t="n">
         <v>5</v>
@@ -9210,10 +9210,10 @@
         <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW40" t="n">
         <v>4</v>
@@ -9222,10 +9222,10 @@
         <v>2</v>
       </c>
       <c r="AY40" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ40" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA40" t="n">
         <v>2</v>
@@ -9428,10 +9428,10 @@
         <v>0</v>
       </c>
       <c r="AU41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW41" t="n">
         <v>4</v>
@@ -9440,10 +9440,10 @@
         <v>3</v>
       </c>
       <c r="AY41" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ41" t="n">
         <v>7</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>8</v>
       </c>
       <c r="BA41" t="n">
         <v>4</v>
@@ -9646,10 +9646,10 @@
         <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW42" t="n">
         <v>16</v>
@@ -9658,10 +9658,10 @@
         <v>3</v>
       </c>
       <c r="AY42" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ42" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA42" t="n">
         <v>5</v>
@@ -9864,10 +9864,10 @@
         <v>0</v>
       </c>
       <c r="AU43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW43" t="n">
         <v>14</v>
@@ -9876,10 +9876,10 @@
         <v>9</v>
       </c>
       <c r="AY43" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ43" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA43" t="n">
         <v>6</v>
@@ -10073,19 +10073,19 @@
         <v>1.83</v>
       </c>
       <c r="AR44" t="n">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="AS44" t="n">
         <v>0</v>
       </c>
       <c r="AT44" t="n">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="AU44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW44" t="n">
         <v>11</v>
@@ -10094,10 +10094,10 @@
         <v>3</v>
       </c>
       <c r="AY44" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA44" t="n">
         <v>4</v>
@@ -10300,10 +10300,10 @@
         <v>0</v>
       </c>
       <c r="AU45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW45" t="n">
         <v>15</v>
@@ -10312,10 +10312,10 @@
         <v>3</v>
       </c>
       <c r="AY45" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA45" t="n">
         <v>6</v>
@@ -10518,10 +10518,10 @@
         <v>0</v>
       </c>
       <c r="AU46" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV46" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW46" t="n">
         <v>4</v>
@@ -10530,10 +10530,10 @@
         <v>8</v>
       </c>
       <c r="AY46" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ46" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA46" t="n">
         <v>7</v>
@@ -10736,10 +10736,10 @@
         <v>0</v>
       </c>
       <c r="AU47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW47" t="n">
         <v>5</v>
@@ -10748,10 +10748,10 @@
         <v>8</v>
       </c>
       <c r="AY47" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ47" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA47" t="n">
         <v>2</v>
@@ -10945,19 +10945,19 @@
         <v>0.67</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AS48" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AT48" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="AU48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW48" t="n">
         <v>4</v>
@@ -10966,10 +10966,10 @@
         <v>20</v>
       </c>
       <c r="AY48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ48" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA48" t="n">
         <v>0</v>
@@ -11163,19 +11163,19 @@
         <v>0.17</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AS49" t="n">
-        <v>0.76</v>
+        <v>0.63</v>
       </c>
       <c r="AT49" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AU49" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW49" t="n">
         <v>10</v>
@@ -11184,10 +11184,10 @@
         <v>6</v>
       </c>
       <c r="AY49" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA49" t="n">
         <v>7</v>
@@ -11381,16 +11381,16 @@
         <v>1</v>
       </c>
       <c r="AR50" t="n">
-        <v>0.68</v>
+        <v>0.54</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AT50" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="AU50" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV50" t="n">
         <v>0</v>
@@ -11399,13 +11399,13 @@
         <v>9</v>
       </c>
       <c r="AX50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY50" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA50" t="n">
         <v>7</v>
@@ -11599,16 +11599,16 @@
         <v>1.1</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.09</v>
+        <v>0.95</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AT51" t="n">
-        <v>2.48</v>
+        <v>2.21</v>
       </c>
       <c r="AU51" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV51" t="n">
         <v>0</v>
@@ -11617,13 +11617,13 @@
         <v>10</v>
       </c>
       <c r="AX51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY51" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA51" t="n">
         <v>6</v>
@@ -11817,19 +11817,19 @@
         <v>1.67</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AS52" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AT52" t="n">
-        <v>2.95</v>
+        <v>2.68</v>
       </c>
       <c r="AU52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW52" t="n">
         <v>6</v>
@@ -11838,10 +11838,10 @@
         <v>4</v>
       </c>
       <c r="AY52" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA52" t="n">
         <v>11</v>
@@ -12035,19 +12035,19 @@
         <v>1.33</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AS53" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="AT53" t="n">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="AU53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW53" t="n">
         <v>12</v>
@@ -12056,10 +12056,10 @@
         <v>8</v>
       </c>
       <c r="AY53" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ53" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA53" t="n">
         <v>3</v>
@@ -12253,19 +12253,19 @@
         <v>1.83</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AT54" t="n">
-        <v>3.82</v>
+        <v>3.55</v>
       </c>
       <c r="AU54" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV54" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW54" t="n">
         <v>13</v>
@@ -12274,10 +12274,10 @@
         <v>5</v>
       </c>
       <c r="AY54" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ54" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA54" t="n">
         <v>6</v>
@@ -12471,19 +12471,19 @@
         <v>1.5</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="AS55" t="n">
-        <v>2.14</v>
+        <v>2.01</v>
       </c>
       <c r="AT55" t="n">
-        <v>3.32</v>
+        <v>3.05</v>
       </c>
       <c r="AU55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW55" t="n">
         <v>7</v>
@@ -12492,10 +12492,10 @@
         <v>8</v>
       </c>
       <c r="AY55" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ55" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA55" t="n">
         <v>6</v>
@@ -12689,19 +12689,19 @@
         <v>1.83</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AS56" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AT56" t="n">
-        <v>3.23</v>
+        <v>2.97</v>
       </c>
       <c r="AU56" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV56" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW56" t="n">
         <v>13</v>
@@ -12710,10 +12710,10 @@
         <v>3</v>
       </c>
       <c r="AY56" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA56" t="n">
         <v>13</v>
@@ -12910,16 +12910,16 @@
         <v>0</v>
       </c>
       <c r="AS57" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AT57" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AU57" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW57" t="n">
         <v>12</v>
@@ -12928,10 +12928,10 @@
         <v>5</v>
       </c>
       <c r="AY57" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ57" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA57" t="n">
         <v>8</v>
@@ -13125,16 +13125,16 @@
         <v>0.67</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AS58" t="n">
         <v>0</v>
       </c>
       <c r="AT58" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AU58" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV58" t="n">
         <v>0</v>
@@ -13143,13 +13143,13 @@
         <v>17</v>
       </c>
       <c r="AX58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY58" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA58" t="n">
         <v>9</v>
@@ -13343,19 +13343,19 @@
         <v>0</v>
       </c>
       <c r="AR59" t="n">
-        <v>0.82</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AS59" t="n">
-        <v>0.83</v>
+        <v>0.7</v>
       </c>
       <c r="AT59" t="n">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="AU59" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW59" t="n">
         <v>15</v>
@@ -13364,10 +13364,10 @@
         <v>7</v>
       </c>
       <c r="AY59" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ59" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA59" t="n">
         <v>5</v>
@@ -13561,19 +13561,19 @@
         <v>1</v>
       </c>
       <c r="AR60" t="n">
-        <v>2.79</v>
+        <v>2.66</v>
       </c>
       <c r="AS60" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AT60" t="n">
-        <v>4.6</v>
+        <v>4.34</v>
       </c>
       <c r="AU60" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV60" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW60" t="n">
         <v>10</v>
@@ -13582,10 +13582,10 @@
         <v>7</v>
       </c>
       <c r="AY60" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA60" t="n">
         <v>12</v>
@@ -13779,19 +13779,19 @@
         <v>1.5</v>
       </c>
       <c r="AR61" t="n">
-        <v>1.02</v>
+        <v>0.89</v>
       </c>
       <c r="AS61" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AT61" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AU61" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV61" t="n">
         <v>6</v>
-      </c>
-      <c r="AV61" t="n">
-        <v>7</v>
       </c>
       <c r="AW61" t="n">
         <v>5</v>
@@ -13800,10 +13800,10 @@
         <v>8</v>
       </c>
       <c r="AY61" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ61" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA61" t="n">
         <v>2</v>
@@ -13997,16 +13997,16 @@
         <v>1.33</v>
       </c>
       <c r="AR62" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AS62" t="n">
-        <v>2.09</v>
+        <v>1.96</v>
       </c>
       <c r="AT62" t="n">
-        <v>3.23</v>
+        <v>2.97</v>
       </c>
       <c r="AU62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV62" t="n">
         <v>0</v>
@@ -14015,13 +14015,13 @@
         <v>9</v>
       </c>
       <c r="AX62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY62" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA62" t="n">
         <v>6</v>
@@ -14215,19 +14215,19 @@
         <v>1.33</v>
       </c>
       <c r="AR63" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AS63" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AT63" t="n">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="AU63" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV63" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW63" t="n">
         <v>18</v>
@@ -14236,10 +14236,10 @@
         <v>8</v>
       </c>
       <c r="AY63" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ63" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA63" t="n">
         <v>8</v>
@@ -14433,19 +14433,19 @@
         <v>1.83</v>
       </c>
       <c r="AR64" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AS64" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AT64" t="n">
-        <v>3.58</v>
+        <v>3.32</v>
       </c>
       <c r="AU64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW64" t="n">
         <v>12</v>
@@ -14454,10 +14454,10 @@
         <v>8</v>
       </c>
       <c r="AY64" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ64" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA64" t="n">
         <v>7</v>
@@ -14651,19 +14651,19 @@
         <v>0.67</v>
       </c>
       <c r="AR65" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="AS65" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AT65" t="n">
-        <v>3.75</v>
+        <v>3.49</v>
       </c>
       <c r="AU65" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW65" t="n">
         <v>8</v>
@@ -14672,10 +14672,10 @@
         <v>8</v>
       </c>
       <c r="AY65" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ65" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA65" t="n">
         <v>6</v>
@@ -14869,19 +14869,19 @@
         <v>1.67</v>
       </c>
       <c r="AR66" t="n">
-        <v>0.88</v>
+        <v>0.74</v>
       </c>
       <c r="AS66" t="n">
-        <v>1.08</v>
+        <v>0.95</v>
       </c>
       <c r="AT66" t="n">
-        <v>1.96</v>
+        <v>1.69</v>
       </c>
       <c r="AU66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW66" t="n">
         <v>6</v>
@@ -14890,10 +14890,10 @@
         <v>8</v>
       </c>
       <c r="AY66" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ66" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA66" t="n">
         <v>3</v>
@@ -15087,19 +15087,19 @@
         <v>1.17</v>
       </c>
       <c r="AR67" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AS67" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AT67" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AU67" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV67" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW67" t="n">
         <v>10</v>
@@ -15108,10 +15108,10 @@
         <v>5</v>
       </c>
       <c r="AY67" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ67" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA67" t="n">
         <v>5</v>
@@ -15305,19 +15305,19 @@
         <v>2.17</v>
       </c>
       <c r="AR68" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AS68" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="AT68" t="n">
-        <v>3.71</v>
+        <v>3.44</v>
       </c>
       <c r="AU68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV68" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW68" t="n">
         <v>8</v>
@@ -15326,10 +15326,10 @@
         <v>7</v>
       </c>
       <c r="AY68" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ68" t="n">
         <v>11</v>
-      </c>
-      <c r="AZ68" t="n">
-        <v>12</v>
       </c>
       <c r="BA68" t="n">
         <v>3</v>
@@ -15523,19 +15523,19 @@
         <v>1.33</v>
       </c>
       <c r="AR69" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AS69" t="n">
-        <v>1.04</v>
+        <v>0.91</v>
       </c>
       <c r="AT69" t="n">
-        <v>2.26</v>
+        <v>2.01</v>
       </c>
       <c r="AU69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW69" t="n">
         <v>12</v>
@@ -15544,10 +15544,10 @@
         <v>8</v>
       </c>
       <c r="AY69" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ69" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA69" t="n">
         <v>7</v>
@@ -15741,19 +15741,19 @@
         <v>1.83</v>
       </c>
       <c r="AR70" t="n">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="AS70" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AT70" t="n">
-        <v>3.97</v>
+        <v>3.71</v>
       </c>
       <c r="AU70" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW70" t="n">
         <v>12</v>
@@ -15762,10 +15762,10 @@
         <v>4</v>
       </c>
       <c r="AY70" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ70" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA70" t="n">
         <v>6</v>
@@ -15959,19 +15959,19 @@
         <v>1.83</v>
       </c>
       <c r="AR71" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="AS71" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AT71" t="n">
-        <v>2.89</v>
+        <v>2.65</v>
       </c>
       <c r="AU71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV71" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW71" t="n">
         <v>10</v>
@@ -15980,10 +15980,10 @@
         <v>15</v>
       </c>
       <c r="AY71" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ71" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA71" t="n">
         <v>4</v>
@@ -16177,19 +16177,19 @@
         <v>2</v>
       </c>
       <c r="AR72" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AS72" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AT72" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="AU72" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV72" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW72" t="n">
         <v>10</v>
@@ -16198,10 +16198,10 @@
         <v>9</v>
       </c>
       <c r="AY72" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ72" t="n">
         <v>15</v>
-      </c>
-      <c r="AZ72" t="n">
-        <v>16</v>
       </c>
       <c r="BA72" t="n">
         <v>3</v>
@@ -16395,19 +16395,19 @@
         <v>2</v>
       </c>
       <c r="AR73" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AS73" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AT73" t="n">
-        <v>3.38</v>
+        <v>3.12</v>
       </c>
       <c r="AU73" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV73" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW73" t="n">
         <v>11</v>
@@ -16416,10 +16416,10 @@
         <v>4</v>
       </c>
       <c r="AY73" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ73" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA73" t="n">
         <v>10</v>
@@ -16613,19 +16613,19 @@
         <v>2.33</v>
       </c>
       <c r="AR74" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AS74" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AT74" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="AU74" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV74" t="n">
         <v>4</v>
-      </c>
-      <c r="AV74" t="n">
-        <v>5</v>
       </c>
       <c r="AW74" t="n">
         <v>10</v>
@@ -16634,10 +16634,10 @@
         <v>4</v>
       </c>
       <c r="AY74" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ74" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA74" t="n">
         <v>6</v>
@@ -16831,19 +16831,19 @@
         <v>1.33</v>
       </c>
       <c r="AR75" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AS75" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AT75" t="n">
-        <v>2.94</v>
+        <v>2.71</v>
       </c>
       <c r="AU75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV75" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW75" t="n">
         <v>14</v>
@@ -16852,10 +16852,10 @@
         <v>6</v>
       </c>
       <c r="AY75" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ75" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA75" t="n">
         <v>4</v>
@@ -17049,19 +17049,19 @@
         <v>0</v>
       </c>
       <c r="AR76" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AS76" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AT76" t="n">
-        <v>2.57</v>
+        <v>2.29</v>
       </c>
       <c r="AU76" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW76" t="n">
         <v>17</v>
@@ -17070,10 +17070,10 @@
         <v>7</v>
       </c>
       <c r="AY76" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ76" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA76" t="n">
         <v>2</v>
@@ -17267,19 +17267,19 @@
         <v>3</v>
       </c>
       <c r="AR77" t="n">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="AS77" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AT77" t="n">
-        <v>4.44</v>
+        <v>4.18</v>
       </c>
       <c r="AU77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV77" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW77" t="n">
         <v>14</v>
@@ -17288,10 +17288,10 @@
         <v>3</v>
       </c>
       <c r="AY77" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ77" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA77" t="n">
         <v>12</v>
@@ -17485,19 +17485,19 @@
         <v>1.5</v>
       </c>
       <c r="AR78" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AS78" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="AT78" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AU78" t="n">
         <v>4</v>
       </c>
-      <c r="AU78" t="n">
-        <v>5</v>
-      </c>
       <c r="AV78" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW78" t="n">
         <v>7</v>
@@ -17506,10 +17506,10 @@
         <v>6</v>
       </c>
       <c r="AY78" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ78" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA78" t="n">
         <v>10</v>
@@ -17703,19 +17703,19 @@
         <v>0.67</v>
       </c>
       <c r="AR79" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AS79" t="n">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="AT79" t="n">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="AU79" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV79" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW79" t="n">
         <v>16</v>
@@ -17724,10 +17724,10 @@
         <v>9</v>
       </c>
       <c r="AY79" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ79" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA79" t="n">
         <v>3</v>
@@ -17921,19 +17921,19 @@
         <v>2.17</v>
       </c>
       <c r="AR80" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AS80" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AT80" t="n">
-        <v>3.83</v>
+        <v>3.56</v>
       </c>
       <c r="AU80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV80" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW80" t="n">
         <v>9</v>
@@ -17942,10 +17942,10 @@
         <v>5</v>
       </c>
       <c r="AY80" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ80" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA80" t="n">
         <v>3</v>
@@ -18139,19 +18139,19 @@
         <v>2</v>
       </c>
       <c r="AR81" t="n">
-        <v>0.89</v>
+        <v>0.76</v>
       </c>
       <c r="AS81" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="AT81" t="n">
-        <v>2.49</v>
+        <v>2.22</v>
       </c>
       <c r="AU81" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV81" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW81" t="n">
         <v>7</v>
@@ -18160,10 +18160,10 @@
         <v>5</v>
       </c>
       <c r="AY81" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ81" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA81" t="n">
         <v>9</v>
@@ -18357,19 +18357,19 @@
         <v>2.33</v>
       </c>
       <c r="AR82" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AS82" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AT82" t="n">
-        <v>3.21</v>
+        <v>2.94</v>
       </c>
       <c r="AU82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV82" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW82" t="n">
         <v>10</v>
@@ -18378,10 +18378,10 @@
         <v>7</v>
       </c>
       <c r="AY82" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ82" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA82" t="n">
         <v>4</v>
@@ -18575,19 +18575,19 @@
         <v>0.83</v>
       </c>
       <c r="AR83" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AS83" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AT83" t="n">
-        <v>2.58</v>
+        <v>2.34</v>
       </c>
       <c r="AU83" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV83" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW83" t="n">
         <v>7</v>
@@ -18596,10 +18596,10 @@
         <v>9</v>
       </c>
       <c r="AY83" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ83" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA83" t="n">
         <v>9</v>
@@ -18793,31 +18793,31 @@
         <v>1.83</v>
       </c>
       <c r="AR84" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AS84" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AT84" t="n">
-        <v>2.65</v>
+        <v>2.41</v>
       </c>
       <c r="AU84" t="n">
         <v>0</v>
       </c>
       <c r="AV84" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX84" t="n">
         <v>8</v>
       </c>
       <c r="AY84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ84" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA84" t="n">
         <v>1</v>
@@ -19011,19 +19011,19 @@
         <v>1.83</v>
       </c>
       <c r="AR85" t="n">
-        <v>1.05</v>
+        <v>0.92</v>
       </c>
       <c r="AS85" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AT85" t="n">
-        <v>2.73</v>
+        <v>2.47</v>
       </c>
       <c r="AU85" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW85" t="n">
         <v>22</v>
@@ -19032,10 +19032,10 @@
         <v>5</v>
       </c>
       <c r="AY85" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AZ85" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA85" t="n">
         <v>9</v>
@@ -19229,19 +19229,19 @@
         <v>1.17</v>
       </c>
       <c r="AR86" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AS86" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AT86" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="AU86" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV86" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW86" t="n">
         <v>8</v>
@@ -19250,10 +19250,10 @@
         <v>6</v>
       </c>
       <c r="AY86" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ86" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA86" t="n">
         <v>6</v>
@@ -19447,19 +19447,19 @@
         <v>2</v>
       </c>
       <c r="AR87" t="n">
-        <v>1.12</v>
+        <v>0.99</v>
       </c>
       <c r="AS87" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AT87" t="n">
-        <v>2.76</v>
+        <v>2.49</v>
       </c>
       <c r="AU87" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV87" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW87" t="n">
         <v>7</v>
@@ -19468,10 +19468,10 @@
         <v>2</v>
       </c>
       <c r="AY87" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ87" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA87" t="n">
         <v>7</v>
@@ -19665,19 +19665,19 @@
         <v>1.83</v>
       </c>
       <c r="AR88" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AS88" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AT88" t="n">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="AU88" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW88" t="n">
         <v>4</v>
@@ -19686,10 +19686,10 @@
         <v>3</v>
       </c>
       <c r="AY88" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ88" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA88" t="n">
         <v>3</v>
@@ -19883,19 +19883,19 @@
         <v>3</v>
       </c>
       <c r="AR89" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AS89" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AT89" t="n">
-        <v>3.89</v>
+        <v>3.62</v>
       </c>
       <c r="AU89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV89" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW89" t="n">
         <v>14</v>
@@ -19904,10 +19904,10 @@
         <v>3</v>
       </c>
       <c r="AY89" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ89" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA89" t="n">
         <v>8</v>
@@ -20101,19 +20101,19 @@
         <v>1</v>
       </c>
       <c r="AR90" t="n">
-        <v>1.09</v>
+        <v>0.99</v>
       </c>
       <c r="AS90" t="n">
-        <v>2.27</v>
+        <v>2.14</v>
       </c>
       <c r="AT90" t="n">
-        <v>3.36</v>
+        <v>3.13</v>
       </c>
       <c r="AU90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW90" t="n">
         <v>3</v>
@@ -20122,10 +20122,10 @@
         <v>15</v>
       </c>
       <c r="AY90" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ90" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA90" t="n">
         <v>2</v>
@@ -20319,19 +20319,19 @@
         <v>0.83</v>
       </c>
       <c r="AR91" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AS91" t="n">
-        <v>2.34</v>
+        <v>2.21</v>
       </c>
       <c r="AT91" t="n">
-        <v>4.16</v>
+        <v>3.9</v>
       </c>
       <c r="AU91" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV91" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW91" t="n">
         <v>4</v>
@@ -20340,10 +20340,10 @@
         <v>9</v>
       </c>
       <c r="AY91" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ91" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA91" t="n">
         <v>4</v>
@@ -20537,19 +20537,19 @@
         <v>1.5</v>
       </c>
       <c r="AR92" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AS92" t="n">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AT92" t="n">
-        <v>3.22</v>
+        <v>2.95</v>
       </c>
       <c r="AU92" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW92" t="n">
         <v>8</v>
@@ -20558,10 +20558,10 @@
         <v>5</v>
       </c>
       <c r="AY92" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ92" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA92" t="n">
         <v>2</v>
@@ -20755,19 +20755,19 @@
         <v>2</v>
       </c>
       <c r="AR93" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AS93" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AT93" t="n">
-        <v>2.94</v>
+        <v>2.69</v>
       </c>
       <c r="AU93" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV93" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW93" t="n">
         <v>8</v>
@@ -20776,10 +20776,10 @@
         <v>4</v>
       </c>
       <c r="AY93" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ93" t="n">
         <v>12</v>
-      </c>
-      <c r="AZ93" t="n">
-        <v>13</v>
       </c>
       <c r="BA93" t="n">
         <v>3</v>
@@ -20973,19 +20973,19 @@
         <v>1.83</v>
       </c>
       <c r="AR94" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AS94" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AT94" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="AU94" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV94" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW94" t="n">
         <v>8</v>
@@ -20994,10 +20994,10 @@
         <v>5</v>
       </c>
       <c r="AY94" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ94" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA94" t="n">
         <v>3</v>
@@ -21191,19 +21191,19 @@
         <v>1.33</v>
       </c>
       <c r="AR95" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AS95" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AT95" t="n">
-        <v>2.68</v>
+        <v>2.42</v>
       </c>
       <c r="AU95" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW95" t="n">
         <v>7</v>
@@ -21212,10 +21212,10 @@
         <v>7</v>
       </c>
       <c r="AY95" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ95" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA95" t="n">
         <v>6</v>
@@ -21409,19 +21409,19 @@
         <v>1.83</v>
       </c>
       <c r="AR96" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AS96" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AT96" t="n">
-        <v>3.36</v>
+        <v>3.09</v>
       </c>
       <c r="AU96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV96" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW96" t="n">
         <v>6</v>
@@ -21430,10 +21430,10 @@
         <v>4</v>
       </c>
       <c r="AY96" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ96" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA96" t="n">
         <v>4</v>
@@ -21627,16 +21627,16 @@
         <v>0.17</v>
       </c>
       <c r="AR97" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AS97" t="n">
-        <v>1.09</v>
+        <v>0.96</v>
       </c>
       <c r="AT97" t="n">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="AU97" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV97" t="n">
         <v>0</v>
@@ -21645,13 +21645,13 @@
         <v>15</v>
       </c>
       <c r="AX97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY97" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA97" t="n">
         <v>8</v>
@@ -21845,19 +21845,19 @@
         <v>1.9</v>
       </c>
       <c r="AR98" t="n">
-        <v>1.05</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS98" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AT98" t="n">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="AU98" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV98" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW98" t="n">
         <v>9</v>
@@ -21866,10 +21866,10 @@
         <v>9</v>
       </c>
       <c r="AY98" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ98" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA98" t="n">
         <v>9</v>
@@ -22063,19 +22063,19 @@
         <v>1</v>
       </c>
       <c r="AR99" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="AS99" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AT99" t="n">
-        <v>3.23</v>
+        <v>2.98</v>
       </c>
       <c r="AU99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW99" t="n">
         <v>15</v>
@@ -22084,10 +22084,10 @@
         <v>7</v>
       </c>
       <c r="AY99" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ99" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA99" t="n">
         <v>11</v>
@@ -22281,19 +22281,19 @@
         <v>0.83</v>
       </c>
       <c r="AR100" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AS100" t="n">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="AT100" t="n">
-        <v>3.65</v>
+        <v>3.39</v>
       </c>
       <c r="AU100" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV100" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW100" t="n">
         <v>14</v>
@@ -22302,10 +22302,10 @@
         <v>8</v>
       </c>
       <c r="AY100" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ100" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA100" t="n">
         <v>5</v>
@@ -22499,19 +22499,19 @@
         <v>1</v>
       </c>
       <c r="AR101" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AS101" t="n">
-        <v>1.05</v>
+        <v>0.95</v>
       </c>
       <c r="AT101" t="n">
-        <v>2.76</v>
+        <v>2.53</v>
       </c>
       <c r="AU101" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW101" t="n">
         <v>10</v>
@@ -22520,10 +22520,10 @@
         <v>3</v>
       </c>
       <c r="AY101" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ101" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA101" t="n">
         <v>4</v>
@@ -22717,19 +22717,19 @@
         <v>1.5</v>
       </c>
       <c r="AR102" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AS102" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AT102" t="n">
-        <v>3.57</v>
+        <v>3.3</v>
       </c>
       <c r="AU102" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW102" t="n">
         <v>9</v>
@@ -22738,10 +22738,10 @@
         <v>4</v>
       </c>
       <c r="AY102" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ102" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA102" t="n">
         <v>7</v>
@@ -22935,19 +22935,19 @@
         <v>2</v>
       </c>
       <c r="AR103" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AS103" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AT103" t="n">
-        <v>3.24</v>
+        <v>2.98</v>
       </c>
       <c r="AU103" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV103" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW103" t="n">
         <v>12</v>
@@ -22956,10 +22956,10 @@
         <v>4</v>
       </c>
       <c r="AY103" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ103" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA103" t="n">
         <v>9</v>
@@ -23153,19 +23153,19 @@
         <v>1.5</v>
       </c>
       <c r="AR104" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AS104" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AT104" t="n">
-        <v>2.69</v>
+        <v>2.43</v>
       </c>
       <c r="AU104" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW104" t="n">
         <v>11</v>
@@ -23174,10 +23174,10 @@
         <v>7</v>
       </c>
       <c r="AY104" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ104" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA104" t="n">
         <v>6</v>
@@ -23371,19 +23371,19 @@
         <v>0.83</v>
       </c>
       <c r="AR105" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AS105" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AT105" t="n">
-        <v>3.39</v>
+        <v>3.13</v>
       </c>
       <c r="AU105" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW105" t="n">
         <v>8</v>
@@ -23392,10 +23392,10 @@
         <v>13</v>
       </c>
       <c r="AY105" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ105" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA105" t="n">
         <v>4</v>
@@ -23589,19 +23589,19 @@
         <v>1.1</v>
       </c>
       <c r="AR106" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AS106" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AT106" t="n">
-        <v>2.62</v>
+        <v>2.37</v>
       </c>
       <c r="AU106" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV106" t="n">
         <v>5</v>
-      </c>
-      <c r="AV106" t="n">
-        <v>6</v>
       </c>
       <c r="AW106" t="n">
         <v>14</v>
@@ -23610,10 +23610,10 @@
         <v>10</v>
       </c>
       <c r="AY106" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ106" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA106" t="n">
         <v>9</v>
@@ -23807,19 +23807,19 @@
         <v>1</v>
       </c>
       <c r="AR107" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AS107" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AT107" t="n">
-        <v>3.9</v>
+        <v>3.64</v>
       </c>
       <c r="AU107" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV107" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW107" t="n">
         <v>8</v>
@@ -23828,10 +23828,10 @@
         <v>2</v>
       </c>
       <c r="AY107" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ107" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA107" t="n">
         <v>8</v>
@@ -24025,19 +24025,19 @@
         <v>1.33</v>
       </c>
       <c r="AR108" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AS108" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AT108" t="n">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="AU108" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV108" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW108" t="n">
         <v>6</v>
@@ -24046,10 +24046,10 @@
         <v>9</v>
       </c>
       <c r="AY108" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ108" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA108" t="n">
         <v>5</v>
@@ -24243,19 +24243,19 @@
         <v>1.83</v>
       </c>
       <c r="AR109" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AS109" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AT109" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="AU109" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV109" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW109" t="n">
         <v>13</v>
@@ -24264,10 +24264,10 @@
         <v>5</v>
       </c>
       <c r="AY109" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ109" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA109" t="n">
         <v>7</v>
@@ -24461,16 +24461,16 @@
         <v>1.83</v>
       </c>
       <c r="AR110" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AS110" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AT110" t="n">
-        <v>2.93</v>
+        <v>2.67</v>
       </c>
       <c r="AU110" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV110" t="n">
         <v>0</v>
@@ -24479,13 +24479,13 @@
         <v>12</v>
       </c>
       <c r="AX110" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY110" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ110" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA110" t="n">
         <v>10</v>
@@ -24679,19 +24679,19 @@
         <v>1.33</v>
       </c>
       <c r="AR111" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AS111" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AT111" t="n">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AU111" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV111" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW111" t="n">
         <v>15</v>
@@ -24700,10 +24700,10 @@
         <v>6</v>
       </c>
       <c r="AY111" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ111" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA111" t="n">
         <v>8</v>
@@ -24897,19 +24897,19 @@
         <v>0.67</v>
       </c>
       <c r="AR112" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AS112" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AT112" t="n">
-        <v>3.41</v>
+        <v>3.14</v>
       </c>
       <c r="AU112" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV112" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW112" t="n">
         <v>6</v>
@@ -24918,10 +24918,10 @@
         <v>10</v>
       </c>
       <c r="AY112" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ112" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA112" t="n">
         <v>0</v>
@@ -25115,19 +25115,19 @@
         <v>1.33</v>
       </c>
       <c r="AR113" t="n">
-        <v>1.1</v>
+        <v>0.97</v>
       </c>
       <c r="AS113" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AT113" t="n">
-        <v>2.68</v>
+        <v>2.41</v>
       </c>
       <c r="AU113" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV113" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW113" t="n">
         <v>9</v>
@@ -25136,10 +25136,10 @@
         <v>8</v>
       </c>
       <c r="AY113" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ113" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA113" t="n">
         <v>6</v>
@@ -25333,19 +25333,19 @@
         <v>1.67</v>
       </c>
       <c r="AR114" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AS114" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AT114" t="n">
-        <v>3.23</v>
+        <v>2.96</v>
       </c>
       <c r="AU114" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW114" t="n">
         <v>11</v>
@@ -25354,10 +25354,10 @@
         <v>16</v>
       </c>
       <c r="AY114" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ114" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA114" t="n">
         <v>4</v>
@@ -25551,19 +25551,19 @@
         <v>0.17</v>
       </c>
       <c r="AR115" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AS115" t="n">
-        <v>0.98</v>
+        <v>0.86</v>
       </c>
       <c r="AT115" t="n">
-        <v>2.51</v>
+        <v>2.26</v>
       </c>
       <c r="AU115" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW115" t="n">
         <v>10</v>
@@ -25572,10 +25572,10 @@
         <v>8</v>
       </c>
       <c r="AY115" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ115" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA115" t="n">
         <v>4</v>
@@ -25769,19 +25769,19 @@
         <v>1.33</v>
       </c>
       <c r="AR116" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AS116" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AT116" t="n">
-        <v>3.36</v>
+        <v>3.1</v>
       </c>
       <c r="AU116" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW116" t="n">
         <v>12</v>
@@ -25790,10 +25790,10 @@
         <v>3</v>
       </c>
       <c r="AY116" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ116" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA116" t="n">
         <v>7</v>
@@ -25987,19 +25987,19 @@
         <v>1.1</v>
       </c>
       <c r="AR117" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AS117" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AT117" t="n">
-        <v>2.68</v>
+        <v>2.42</v>
       </c>
       <c r="AU117" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV117" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW117" t="n">
         <v>12</v>
@@ -26008,10 +26008,10 @@
         <v>7</v>
       </c>
       <c r="AY117" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ117" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA117" t="n">
         <v>7</v>
@@ -26205,28 +26205,28 @@
         <v>1.5</v>
       </c>
       <c r="AR118" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AS118" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AT118" t="n">
-        <v>3.31</v>
+        <v>3.05</v>
       </c>
       <c r="AU118" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV118" t="n">
         <v>6</v>
       </c>
-      <c r="AV118" t="n">
+      <c r="AW118" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX118" t="n">
         <v>7</v>
       </c>
-      <c r="AW118" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX118" t="n">
-        <v>6</v>
-      </c>
       <c r="AY118" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ118" t="n">
         <v>13</v>
@@ -26423,19 +26423,19 @@
         <v>1.5</v>
       </c>
       <c r="AR119" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AS119" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AT119" t="n">
-        <v>3.15</v>
+        <v>2.89</v>
       </c>
       <c r="AU119" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV119" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW119" t="n">
         <v>3</v>
@@ -26444,10 +26444,10 @@
         <v>7</v>
       </c>
       <c r="AY119" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ119" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA119" t="n">
         <v>6</v>
@@ -26641,31 +26641,31 @@
         <v>0.67</v>
       </c>
       <c r="AR120" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AS120" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AT120" t="n">
-        <v>3.27</v>
+        <v>3.02</v>
       </c>
       <c r="AU120" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW120" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AX120" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AY120" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AZ120" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BA120" t="n">
         <v>5</v>
@@ -26859,19 +26859,19 @@
         <v>1.9</v>
       </c>
       <c r="AR121" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AS121" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AT121" t="n">
-        <v>3.75</v>
+        <v>3.48</v>
       </c>
       <c r="AU121" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV121" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW121" t="n">
         <v>14</v>
@@ -26880,10 +26880,10 @@
         <v>4</v>
       </c>
       <c r="AY121" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ121" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA121" t="n">
         <v>7</v>
@@ -27077,19 +27077,19 @@
         <v>1.83</v>
       </c>
       <c r="AR122" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AS122" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AT122" t="n">
-        <v>2.98</v>
+        <v>2.73</v>
       </c>
       <c r="AU122" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV122" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW122" t="n">
         <v>9</v>
@@ -27098,10 +27098,10 @@
         <v>7</v>
       </c>
       <c r="AY122" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ122" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA122" t="n">
         <v>5</v>
@@ -27295,19 +27295,19 @@
         <v>0</v>
       </c>
       <c r="AR123" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AS123" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AT123" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="AU123" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW123" t="n">
         <v>7</v>
@@ -27316,10 +27316,10 @@
         <v>4</v>
       </c>
       <c r="AY123" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ123" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA123" t="n">
         <v>4</v>
@@ -27513,19 +27513,19 @@
         <v>1.83</v>
       </c>
       <c r="AR124" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS124" t="n">
         <v>1.7</v>
       </c>
-      <c r="AS124" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AT124" t="n">
-        <v>3.54</v>
+        <v>3.27</v>
       </c>
       <c r="AU124" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV124" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW124" t="n">
         <v>10</v>
@@ -27534,10 +27534,10 @@
         <v>3</v>
       </c>
       <c r="AY124" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ124" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA124" t="n">
         <v>3</v>
@@ -27731,19 +27731,19 @@
         <v>1</v>
       </c>
       <c r="AR125" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AS125" t="n">
-        <v>0.96</v>
+        <v>0.86</v>
       </c>
       <c r="AT125" t="n">
-        <v>3.03</v>
+        <v>2.8</v>
       </c>
       <c r="AU125" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV125" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW125" t="n">
         <v>12</v>
@@ -27752,10 +27752,10 @@
         <v>3</v>
       </c>
       <c r="AY125" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ125" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA125" t="n">
         <v>9</v>
@@ -27949,31 +27949,31 @@
         <v>1.33</v>
       </c>
       <c r="AR126" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AS126" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AT126" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="AU126" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV126" t="n">
         <v>0</v>
       </c>
       <c r="AW126" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AX126" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY126" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AZ126" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA126" t="n">
         <v>7</v>
@@ -28167,28 +28167,28 @@
         <v>1</v>
       </c>
       <c r="AR127" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AS127" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AT127" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="AU127" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW127" t="n">
         <v>7</v>
       </c>
-      <c r="AV127" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW127" t="n">
-        <v>5</v>
-      </c>
       <c r="AX127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY127" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ127" t="n">
         <v>8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South America Copa Libertadores_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South America Copa Libertadores_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="273">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -637,6 +637,12 @@
     <t>['26']</t>
   </si>
   <si>
+    <t>['78']</t>
+  </si>
+  <si>
+    <t>['28']</t>
+  </si>
+  <si>
     <t>['90+9']</t>
   </si>
   <si>
@@ -656,9 +662,6 @@
   </si>
   <si>
     <t>['69']</t>
-  </si>
-  <si>
-    <t>['78']</t>
   </si>
   <si>
     <t>['14', '33', '45+3', '63']</t>
@@ -793,9 +796,6 @@
     <t>['7', '26', '48']</t>
   </si>
   <si>
-    <t>['28']</t>
-  </si>
-  <si>
     <t>['20', '76']</t>
   </si>
   <si>
@@ -830,6 +830,9 @@
   </si>
   <si>
     <t>['54']</t>
+  </si>
+  <si>
+    <t>['90+8']</t>
   </si>
 </sst>
 </file>
@@ -1191,7 +1194,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP127"/>
+  <dimension ref="A1:BP132"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1653,7 +1656,7 @@
         <v>118</v>
       </c>
       <c r="P3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q3">
         <v>3</v>
@@ -1859,7 +1862,7 @@
         <v>119</v>
       </c>
       <c r="P4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q4">
         <v>3.25</v>
@@ -2065,7 +2068,7 @@
         <v>120</v>
       </c>
       <c r="P5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q5">
         <v>2</v>
@@ -2271,7 +2274,7 @@
         <v>121</v>
       </c>
       <c r="P6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q6">
         <v>2.2</v>
@@ -2477,7 +2480,7 @@
         <v>122</v>
       </c>
       <c r="P7" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q7">
         <v>1.8</v>
@@ -2683,7 +2686,7 @@
         <v>123</v>
       </c>
       <c r="P8" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3095,7 +3098,7 @@
         <v>125</v>
       </c>
       <c r="P10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q10">
         <v>2.05</v>
@@ -3713,7 +3716,7 @@
         <v>120</v>
       </c>
       <c r="P13" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="Q13">
         <v>3.2</v>
@@ -3919,7 +3922,7 @@
         <v>120</v>
       </c>
       <c r="P14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -4000,7 +4003,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ14">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR14">
         <v>1.46</v>
@@ -4331,7 +4334,7 @@
         <v>128</v>
       </c>
       <c r="P16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q16">
         <v>2.28</v>
@@ -4537,7 +4540,7 @@
         <v>129</v>
       </c>
       <c r="P17" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q17">
         <v>1.87</v>
@@ -4949,7 +4952,7 @@
         <v>131</v>
       </c>
       <c r="P19" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q19">
         <v>2.5</v>
@@ -5155,7 +5158,7 @@
         <v>132</v>
       </c>
       <c r="P20" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q20">
         <v>1.83</v>
@@ -5361,7 +5364,7 @@
         <v>133</v>
       </c>
       <c r="P21" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q21">
         <v>1.33</v>
@@ -5645,7 +5648,7 @@
         <v>2</v>
       </c>
       <c r="AP22">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ22">
         <v>1.5</v>
@@ -5979,7 +5982,7 @@
         <v>136</v>
       </c>
       <c r="P24" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q24">
         <v>3.6</v>
@@ -6266,7 +6269,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ25">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR25">
         <v>0.91</v>
@@ -7009,7 +7012,7 @@
         <v>139</v>
       </c>
       <c r="P29" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q29">
         <v>2.3</v>
@@ -7087,7 +7090,7 @@
         <v>2</v>
       </c>
       <c r="AP29">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ29">
         <v>1.5</v>
@@ -7627,7 +7630,7 @@
         <v>120</v>
       </c>
       <c r="P32" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q32">
         <v>4.8</v>
@@ -7708,7 +7711,7 @@
         <v>0.17</v>
       </c>
       <c r="AQ32">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AR32">
         <v>0</v>
@@ -7833,7 +7836,7 @@
         <v>142</v>
       </c>
       <c r="P33" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q33">
         <v>2.2</v>
@@ -7911,7 +7914,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ33">
         <v>1</v>
@@ -8039,7 +8042,7 @@
         <v>120</v>
       </c>
       <c r="P34" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q34">
         <v>2.7</v>
@@ -8117,10 +8120,10 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ34">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AR34">
         <v>0</v>
@@ -8245,7 +8248,7 @@
         <v>143</v>
       </c>
       <c r="P35" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q35">
         <v>4</v>
@@ -8451,7 +8454,7 @@
         <v>120</v>
       </c>
       <c r="P36" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q36">
         <v>3.1</v>
@@ -8863,7 +8866,7 @@
         <v>145</v>
       </c>
       <c r="P38" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q38">
         <v>5.5</v>
@@ -9069,7 +9072,7 @@
         <v>146</v>
       </c>
       <c r="P39" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q39">
         <v>2.75</v>
@@ -9147,10 +9150,10 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AQ39">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AR39">
         <v>0</v>
@@ -9356,7 +9359,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ40">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AR40">
         <v>0</v>
@@ -9481,7 +9484,7 @@
         <v>120</v>
       </c>
       <c r="P41" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q41">
         <v>4.33</v>
@@ -9971,7 +9974,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AQ43">
         <v>1.17</v>
@@ -10305,7 +10308,7 @@
         <v>148</v>
       </c>
       <c r="P45" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q45">
         <v>3</v>
@@ -10386,7 +10389,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ45">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR45">
         <v>1.99</v>
@@ -10511,7 +10514,7 @@
         <v>149</v>
       </c>
       <c r="P46" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q46">
         <v>6</v>
@@ -10717,7 +10720,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q47">
         <v>7</v>
@@ -10798,7 +10801,7 @@
         <v>0</v>
       </c>
       <c r="AQ47">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AR47">
         <v>0</v>
@@ -11413,7 +11416,7 @@
         <v>3</v>
       </c>
       <c r="AP50">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ50">
         <v>1</v>
@@ -11541,7 +11544,7 @@
         <v>153</v>
       </c>
       <c r="P51" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -11619,7 +11622,7 @@
         <v>3</v>
       </c>
       <c r="AP51">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ51">
         <v>1.67</v>
@@ -12159,7 +12162,7 @@
         <v>120</v>
       </c>
       <c r="P54" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q54">
         <v>3.25</v>
@@ -12240,7 +12243,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ54">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AR54">
         <v>1.78</v>
@@ -12365,7 +12368,7 @@
         <v>120</v>
       </c>
       <c r="P55" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q55">
         <v>3.5</v>
@@ -12571,7 +12574,7 @@
         <v>155</v>
       </c>
       <c r="P56" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q56">
         <v>1.8</v>
@@ -12649,7 +12652,7 @@
         <v>1</v>
       </c>
       <c r="AP56">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ56">
         <v>1.83</v>
@@ -13064,7 +13067,7 @@
         <v>3</v>
       </c>
       <c r="AQ58">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR58">
         <v>0</v>
@@ -13395,7 +13398,7 @@
         <v>159</v>
       </c>
       <c r="P60" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q60">
         <v>1.91</v>
@@ -13473,7 +13476,7 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ60">
         <v>1</v>
@@ -13679,10 +13682,10 @@
         <v>3</v>
       </c>
       <c r="AP61">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AQ61">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR61">
         <v>0.89</v>
@@ -13807,7 +13810,7 @@
         <v>120</v>
       </c>
       <c r="P62" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q62">
         <v>3</v>
@@ -13888,7 +13891,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ62">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR62">
         <v>1.01</v>
@@ -14013,7 +14016,7 @@
         <v>161</v>
       </c>
       <c r="P63" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q63">
         <v>1.91</v>
@@ -14091,7 +14094,7 @@
         <v>1.57</v>
       </c>
       <c r="AP63">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AQ63">
         <v>1.33</v>
@@ -14506,7 +14509,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ65">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AR65">
         <v>1.57</v>
@@ -14631,7 +14634,7 @@
         <v>163</v>
       </c>
       <c r="P66" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14837,7 +14840,7 @@
         <v>164</v>
       </c>
       <c r="P67" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -14915,7 +14918,7 @@
         <v>0</v>
       </c>
       <c r="AP67">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AQ67">
         <v>1.17</v>
@@ -15124,7 +15127,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ68">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AR68">
         <v>1.16</v>
@@ -15249,7 +15252,7 @@
         <v>120</v>
       </c>
       <c r="P69" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q69">
         <v>2.38</v>
@@ -15536,7 +15539,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ70">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AR70">
         <v>2.18</v>
@@ -15742,7 +15745,7 @@
         <v>1</v>
       </c>
       <c r="AQ71">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AR71">
         <v>1.09</v>
@@ -15867,7 +15870,7 @@
         <v>120</v>
       </c>
       <c r="P72" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q72">
         <v>4</v>
@@ -15948,7 +15951,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ72">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AR72">
         <v>1.07</v>
@@ -16073,7 +16076,7 @@
         <v>166</v>
       </c>
       <c r="P73" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q73">
         <v>3.2</v>
@@ -16357,7 +16360,7 @@
         <v>1.5</v>
       </c>
       <c r="AP74">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ74">
         <v>2</v>
@@ -16485,7 +16488,7 @@
         <v>167</v>
       </c>
       <c r="P75" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q75">
         <v>3.6</v>
@@ -16566,7 +16569,7 @@
         <v>1</v>
       </c>
       <c r="AQ75">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR75">
         <v>1.54</v>
@@ -16691,7 +16694,7 @@
         <v>168</v>
       </c>
       <c r="P76" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q76">
         <v>1.91</v>
@@ -16897,7 +16900,7 @@
         <v>169</v>
       </c>
       <c r="P77" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q77">
         <v>2.6</v>
@@ -17184,7 +17187,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ78">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR78">
         <v>1.85</v>
@@ -17309,7 +17312,7 @@
         <v>171</v>
       </c>
       <c r="P79" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q79">
         <v>2.4</v>
@@ -17387,7 +17390,7 @@
         <v>0</v>
       </c>
       <c r="AP79">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ79">
         <v>0.67</v>
@@ -17515,7 +17518,7 @@
         <v>120</v>
       </c>
       <c r="P80" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -17596,7 +17599,7 @@
         <v>1</v>
       </c>
       <c r="AQ80">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AR80">
         <v>1.6</v>
@@ -17721,7 +17724,7 @@
         <v>172</v>
       </c>
       <c r="P81" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q81">
         <v>8</v>
@@ -17927,7 +17930,7 @@
         <v>120</v>
       </c>
       <c r="P82" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q82">
         <v>4</v>
@@ -18008,7 +18011,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ82">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AR82">
         <v>1.46</v>
@@ -18211,7 +18214,7 @@
         <v>0.67</v>
       </c>
       <c r="AP83">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ83">
         <v>0.83</v>
@@ -18339,7 +18342,7 @@
         <v>120</v>
       </c>
       <c r="P84" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q84">
         <v>4.33</v>
@@ -18420,7 +18423,7 @@
         <v>1</v>
       </c>
       <c r="AQ84">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AR84">
         <v>1.12</v>
@@ -18545,7 +18548,7 @@
         <v>174</v>
       </c>
       <c r="P85" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q85">
         <v>2.05</v>
@@ -18751,7 +18754,7 @@
         <v>175</v>
       </c>
       <c r="P86" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q86">
         <v>4.75</v>
@@ -18957,7 +18960,7 @@
         <v>120</v>
       </c>
       <c r="P87" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q87">
         <v>3.1</v>
@@ -19038,7 +19041,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ87">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AR87">
         <v>0.99</v>
@@ -19163,7 +19166,7 @@
         <v>176</v>
       </c>
       <c r="P88" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q88">
         <v>6</v>
@@ -19244,7 +19247,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ88">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AR88">
         <v>1.66</v>
@@ -19369,7 +19372,7 @@
         <v>120</v>
       </c>
       <c r="P89" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q89">
         <v>5</v>
@@ -19447,7 +19450,7 @@
         <v>3</v>
       </c>
       <c r="AP89">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ89">
         <v>3</v>
@@ -19859,7 +19862,7 @@
         <v>0.33</v>
       </c>
       <c r="AP91">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AQ91">
         <v>0.83</v>
@@ -20193,7 +20196,7 @@
         <v>179</v>
       </c>
       <c r="P93" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20271,10 +20274,10 @@
         <v>1.67</v>
       </c>
       <c r="AP93">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AQ93">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR93">
         <v>1.65</v>
@@ -20399,7 +20402,7 @@
         <v>180</v>
       </c>
       <c r="P94" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q94">
         <v>4.75</v>
@@ -20605,7 +20608,7 @@
         <v>181</v>
       </c>
       <c r="P95" t="s">
-        <v>259</v>
+        <v>208</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21095,7 +21098,7 @@
         <v>1.25</v>
       </c>
       <c r="AP97">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ97">
         <v>1</v>
@@ -21304,7 +21307,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ98">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR98">
         <v>0.9399999999999999</v>
@@ -21713,7 +21716,7 @@
         <v>0.5</v>
       </c>
       <c r="AP100">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ100">
         <v>0.83</v>
@@ -21919,7 +21922,7 @@
         <v>1.5</v>
       </c>
       <c r="AP101">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AQ101">
         <v>1</v>
@@ -22125,7 +22128,7 @@
         <v>1.88</v>
       </c>
       <c r="AP102">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AQ102">
         <v>1.5</v>
@@ -22334,7 +22337,7 @@
         <v>2</v>
       </c>
       <c r="AQ103">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AR103">
         <v>1.46</v>
@@ -22537,7 +22540,7 @@
         <v>1.75</v>
       </c>
       <c r="AP104">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AQ104">
         <v>1.5</v>
@@ -22743,7 +22746,7 @@
         <v>0.5</v>
       </c>
       <c r="AP105">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ105">
         <v>0.83</v>
@@ -23364,7 +23367,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ108">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR108">
         <v>1.31</v>
@@ -23773,7 +23776,7 @@
         <v>2</v>
       </c>
       <c r="AP110">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ110">
         <v>1.83</v>
@@ -24185,7 +24188,7 @@
         <v>0.8</v>
       </c>
       <c r="AP112">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AQ112">
         <v>0.67</v>
@@ -24803,7 +24806,7 @@
         <v>0.2</v>
       </c>
       <c r="AP115">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ115">
         <v>0.17</v>
@@ -25424,7 +25427,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ118">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR118">
         <v>1.36</v>
@@ -25627,7 +25630,7 @@
         <v>1.67</v>
       </c>
       <c r="AP119">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AQ119">
         <v>1.5</v>
@@ -25833,7 +25836,7 @@
         <v>0</v>
       </c>
       <c r="AP120">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ120">
         <v>0</v>
@@ -26248,7 +26251,7 @@
         <v>1</v>
       </c>
       <c r="AQ122">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR122">
         <v>1.77</v>
@@ -26863,10 +26866,10 @@
         <v>2</v>
       </c>
       <c r="AP125">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ125">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AR125">
         <v>1.57</v>
@@ -27069,10 +27072,10 @@
         <v>1.6</v>
       </c>
       <c r="AP126">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ126">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR126">
         <v>1.75</v>
@@ -27354,6 +27357,1036 @@
       </c>
       <c r="BP127">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="128" spans="1:68">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>7919108</v>
+      </c>
+      <c r="C128" t="s">
+        <v>68</v>
+      </c>
+      <c r="D128" t="s">
+        <v>69</v>
+      </c>
+      <c r="E128" s="2">
+        <v>45881.79166666666</v>
+      </c>
+      <c r="F128">
+        <v>0</v>
+      </c>
+      <c r="G128" t="s">
+        <v>90</v>
+      </c>
+      <c r="H128" t="s">
+        <v>93</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
+        <v>0</v>
+      </c>
+      <c r="K128">
+        <v>0</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128">
+        <v>0</v>
+      </c>
+      <c r="N128">
+        <v>0</v>
+      </c>
+      <c r="O128" t="s">
+        <v>120</v>
+      </c>
+      <c r="P128" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q128">
+        <v>2.7</v>
+      </c>
+      <c r="R128">
+        <v>1.9</v>
+      </c>
+      <c r="S128">
+        <v>4.4</v>
+      </c>
+      <c r="T128">
+        <v>1.52</v>
+      </c>
+      <c r="U128">
+        <v>2.35</v>
+      </c>
+      <c r="V128">
+        <v>3.3</v>
+      </c>
+      <c r="W128">
+        <v>1.28</v>
+      </c>
+      <c r="X128">
+        <v>9.5</v>
+      </c>
+      <c r="Y128">
+        <v>1.05</v>
+      </c>
+      <c r="Z128">
+        <v>1.95</v>
+      </c>
+      <c r="AA128">
+        <v>3</v>
+      </c>
+      <c r="AB128">
+        <v>3.65</v>
+      </c>
+      <c r="AC128">
+        <v>1.1</v>
+      </c>
+      <c r="AD128">
+        <v>6.25</v>
+      </c>
+      <c r="AE128">
+        <v>1.55</v>
+      </c>
+      <c r="AF128">
+        <v>2.4</v>
+      </c>
+      <c r="AG128">
+        <v>2.55</v>
+      </c>
+      <c r="AH128">
+        <v>1.45</v>
+      </c>
+      <c r="AI128">
+        <v>2.1</v>
+      </c>
+      <c r="AJ128">
+        <v>1.65</v>
+      </c>
+      <c r="AK128">
+        <v>1.24</v>
+      </c>
+      <c r="AL128">
+        <v>1.35</v>
+      </c>
+      <c r="AM128">
+        <v>1.73</v>
+      </c>
+      <c r="AN128">
+        <v>1.33</v>
+      </c>
+      <c r="AO128">
+        <v>1.83</v>
+      </c>
+      <c r="AP128">
+        <v>1.29</v>
+      </c>
+      <c r="AQ128">
+        <v>1.71</v>
+      </c>
+      <c r="AR128">
+        <v>1.49</v>
+      </c>
+      <c r="AS128">
+        <v>1.7</v>
+      </c>
+      <c r="AT128">
+        <v>3.19</v>
+      </c>
+      <c r="AU128">
+        <v>1</v>
+      </c>
+      <c r="AV128">
+        <v>3</v>
+      </c>
+      <c r="AW128">
+        <v>12</v>
+      </c>
+      <c r="AX128">
+        <v>10</v>
+      </c>
+      <c r="AY128">
+        <v>13</v>
+      </c>
+      <c r="AZ128">
+        <v>13</v>
+      </c>
+      <c r="BA128">
+        <v>5</v>
+      </c>
+      <c r="BB128">
+        <v>5</v>
+      </c>
+      <c r="BC128">
+        <v>10</v>
+      </c>
+      <c r="BD128">
+        <v>1.61</v>
+      </c>
+      <c r="BE128">
+        <v>8.6</v>
+      </c>
+      <c r="BF128">
+        <v>2.81</v>
+      </c>
+      <c r="BG128">
+        <v>1.27</v>
+      </c>
+      <c r="BH128">
+        <v>3.14</v>
+      </c>
+      <c r="BI128">
+        <v>1.53</v>
+      </c>
+      <c r="BJ128">
+        <v>2.28</v>
+      </c>
+      <c r="BK128">
+        <v>1.91</v>
+      </c>
+      <c r="BL128">
+        <v>1.73</v>
+      </c>
+      <c r="BM128">
+        <v>2.5</v>
+      </c>
+      <c r="BN128">
+        <v>1.44</v>
+      </c>
+      <c r="BO128">
+        <v>3.34</v>
+      </c>
+      <c r="BP128">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="129" spans="1:68">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129">
+        <v>7919109</v>
+      </c>
+      <c r="C129" t="s">
+        <v>68</v>
+      </c>
+      <c r="D129" t="s">
+        <v>69</v>
+      </c>
+      <c r="E129" s="2">
+        <v>45881.89583333334</v>
+      </c>
+      <c r="F129">
+        <v>0</v>
+      </c>
+      <c r="G129" t="s">
+        <v>103</v>
+      </c>
+      <c r="H129" t="s">
+        <v>113</v>
+      </c>
+      <c r="I129">
+        <v>0</v>
+      </c>
+      <c r="J129">
+        <v>0</v>
+      </c>
+      <c r="K129">
+        <v>0</v>
+      </c>
+      <c r="L129">
+        <v>1</v>
+      </c>
+      <c r="M129">
+        <v>0</v>
+      </c>
+      <c r="N129">
+        <v>1</v>
+      </c>
+      <c r="O129" t="s">
+        <v>207</v>
+      </c>
+      <c r="P129" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q129">
+        <v>3.5</v>
+      </c>
+      <c r="R129">
+        <v>1.95</v>
+      </c>
+      <c r="S129">
+        <v>3.5</v>
+      </c>
+      <c r="T129">
+        <v>1.53</v>
+      </c>
+      <c r="U129">
+        <v>2.38</v>
+      </c>
+      <c r="V129">
+        <v>3.5</v>
+      </c>
+      <c r="W129">
+        <v>1.29</v>
+      </c>
+      <c r="X129">
+        <v>11</v>
+      </c>
+      <c r="Y129">
+        <v>1.05</v>
+      </c>
+      <c r="Z129">
+        <v>2.56</v>
+      </c>
+      <c r="AA129">
+        <v>2.83</v>
+      </c>
+      <c r="AB129">
+        <v>2.67</v>
+      </c>
+      <c r="AC129">
+        <v>1.1</v>
+      </c>
+      <c r="AD129">
+        <v>6.5</v>
+      </c>
+      <c r="AE129">
+        <v>1.53</v>
+      </c>
+      <c r="AF129">
+        <v>2.25</v>
+      </c>
+      <c r="AG129">
+        <v>2.48</v>
+      </c>
+      <c r="AH129">
+        <v>1.47</v>
+      </c>
+      <c r="AI129">
+        <v>2.05</v>
+      </c>
+      <c r="AJ129">
+        <v>1.7</v>
+      </c>
+      <c r="AK129">
+        <v>1.42</v>
+      </c>
+      <c r="AL129">
+        <v>1.33</v>
+      </c>
+      <c r="AM129">
+        <v>1.45</v>
+      </c>
+      <c r="AN129">
+        <v>1.83</v>
+      </c>
+      <c r="AO129">
+        <v>2.17</v>
+      </c>
+      <c r="AP129">
+        <v>2</v>
+      </c>
+      <c r="AQ129">
+        <v>1.86</v>
+      </c>
+      <c r="AR129">
+        <v>1.57</v>
+      </c>
+      <c r="AS129">
+        <v>1.75</v>
+      </c>
+      <c r="AT129">
+        <v>3.32</v>
+      </c>
+      <c r="AU129">
+        <v>3</v>
+      </c>
+      <c r="AV129">
+        <v>0</v>
+      </c>
+      <c r="AW129">
+        <v>10</v>
+      </c>
+      <c r="AX129">
+        <v>9</v>
+      </c>
+      <c r="AY129">
+        <v>13</v>
+      </c>
+      <c r="AZ129">
+        <v>9</v>
+      </c>
+      <c r="BA129">
+        <v>4</v>
+      </c>
+      <c r="BB129">
+        <v>1</v>
+      </c>
+      <c r="BC129">
+        <v>5</v>
+      </c>
+      <c r="BD129">
+        <v>1.95</v>
+      </c>
+      <c r="BE129">
+        <v>8</v>
+      </c>
+      <c r="BF129">
+        <v>2.05</v>
+      </c>
+      <c r="BG129">
+        <v>1.38</v>
+      </c>
+      <c r="BH129">
+        <v>2.71</v>
+      </c>
+      <c r="BI129">
+        <v>1.73</v>
+      </c>
+      <c r="BJ129">
+        <v>2</v>
+      </c>
+      <c r="BK129">
+        <v>2</v>
+      </c>
+      <c r="BL129">
+        <v>1.67</v>
+      </c>
+      <c r="BM129">
+        <v>2.88</v>
+      </c>
+      <c r="BN129">
+        <v>1.32</v>
+      </c>
+      <c r="BO129">
+        <v>3.75</v>
+      </c>
+      <c r="BP129">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="130" spans="1:68">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>7919110</v>
+      </c>
+      <c r="C130" t="s">
+        <v>68</v>
+      </c>
+      <c r="D130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E130" s="2">
+        <v>45881.89583333334</v>
+      </c>
+      <c r="F130">
+        <v>0</v>
+      </c>
+      <c r="G130" t="s">
+        <v>97</v>
+      </c>
+      <c r="H130" t="s">
+        <v>116</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="J130">
+        <v>0</v>
+      </c>
+      <c r="K130">
+        <v>0</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="M130">
+        <v>0</v>
+      </c>
+      <c r="N130">
+        <v>0</v>
+      </c>
+      <c r="O130" t="s">
+        <v>120</v>
+      </c>
+      <c r="P130" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q130">
+        <v>3</v>
+      </c>
+      <c r="R130">
+        <v>1.95</v>
+      </c>
+      <c r="S130">
+        <v>4.5</v>
+      </c>
+      <c r="T130">
+        <v>1.53</v>
+      </c>
+      <c r="U130">
+        <v>2.38</v>
+      </c>
+      <c r="V130">
+        <v>3.75</v>
+      </c>
+      <c r="W130">
+        <v>1.25</v>
+      </c>
+      <c r="X130">
+        <v>11</v>
+      </c>
+      <c r="Y130">
+        <v>1.05</v>
+      </c>
+      <c r="Z130">
+        <v>2.03</v>
+      </c>
+      <c r="AA130">
+        <v>2.91</v>
+      </c>
+      <c r="AB130">
+        <v>3.52</v>
+      </c>
+      <c r="AC130">
+        <v>1.12</v>
+      </c>
+      <c r="AD130">
+        <v>6</v>
+      </c>
+      <c r="AE130">
+        <v>1.55</v>
+      </c>
+      <c r="AF130">
+        <v>2.45</v>
+      </c>
+      <c r="AG130">
+        <v>2.43</v>
+      </c>
+      <c r="AH130">
+        <v>1.49</v>
+      </c>
+      <c r="AI130">
+        <v>2.2</v>
+      </c>
+      <c r="AJ130">
+        <v>1.62</v>
+      </c>
+      <c r="AK130">
+        <v>1.25</v>
+      </c>
+      <c r="AL130">
+        <v>1.33</v>
+      </c>
+      <c r="AM130">
+        <v>1.65</v>
+      </c>
+      <c r="AN130">
+        <v>1.5</v>
+      </c>
+      <c r="AO130">
+        <v>2.33</v>
+      </c>
+      <c r="AP130">
+        <v>1.43</v>
+      </c>
+      <c r="AQ130">
+        <v>2.14</v>
+      </c>
+      <c r="AR130">
+        <v>1.53</v>
+      </c>
+      <c r="AS130">
+        <v>1.34</v>
+      </c>
+      <c r="AT130">
+        <v>2.87</v>
+      </c>
+      <c r="AU130">
+        <v>1</v>
+      </c>
+      <c r="AV130">
+        <v>0</v>
+      </c>
+      <c r="AW130">
+        <v>18</v>
+      </c>
+      <c r="AX130">
+        <v>6</v>
+      </c>
+      <c r="AY130">
+        <v>19</v>
+      </c>
+      <c r="AZ130">
+        <v>6</v>
+      </c>
+      <c r="BA130">
+        <v>8</v>
+      </c>
+      <c r="BB130">
+        <v>3</v>
+      </c>
+      <c r="BC130">
+        <v>11</v>
+      </c>
+      <c r="BD130">
+        <v>1.44</v>
+      </c>
+      <c r="BE130">
+        <v>9</v>
+      </c>
+      <c r="BF130">
+        <v>3.1</v>
+      </c>
+      <c r="BG130">
+        <v>1.29</v>
+      </c>
+      <c r="BH130">
+        <v>3.04</v>
+      </c>
+      <c r="BI130">
+        <v>1.56</v>
+      </c>
+      <c r="BJ130">
+        <v>2.21</v>
+      </c>
+      <c r="BK130">
+        <v>2</v>
+      </c>
+      <c r="BL130">
+        <v>1.73</v>
+      </c>
+      <c r="BM130">
+        <v>2.6</v>
+      </c>
+      <c r="BN130">
+        <v>1.41</v>
+      </c>
+      <c r="BO130">
+        <v>3.5</v>
+      </c>
+      <c r="BP130">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="131" spans="1:68">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131">
+        <v>8172520</v>
+      </c>
+      <c r="C131" t="s">
+        <v>68</v>
+      </c>
+      <c r="D131" t="s">
+        <v>69</v>
+      </c>
+      <c r="E131" s="2">
+        <v>45882.79166666666</v>
+      </c>
+      <c r="F131">
+        <v>0</v>
+      </c>
+      <c r="G131" t="s">
+        <v>87</v>
+      </c>
+      <c r="H131" t="s">
+        <v>104</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131">
+        <v>0</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+      <c r="M131">
+        <v>1</v>
+      </c>
+      <c r="N131">
+        <v>1</v>
+      </c>
+      <c r="O131" t="s">
+        <v>120</v>
+      </c>
+      <c r="P131" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q131">
+        <v>3.4</v>
+      </c>
+      <c r="R131">
+        <v>1.95</v>
+      </c>
+      <c r="S131">
+        <v>3.6</v>
+      </c>
+      <c r="T131">
+        <v>1.53</v>
+      </c>
+      <c r="U131">
+        <v>2.38</v>
+      </c>
+      <c r="V131">
+        <v>3.5</v>
+      </c>
+      <c r="W131">
+        <v>1.29</v>
+      </c>
+      <c r="X131">
+        <v>11</v>
+      </c>
+      <c r="Y131">
+        <v>1.05</v>
+      </c>
+      <c r="Z131">
+        <v>2.49</v>
+      </c>
+      <c r="AA131">
+        <v>2.87</v>
+      </c>
+      <c r="AB131">
+        <v>2.7</v>
+      </c>
+      <c r="AC131">
+        <v>1.11</v>
+      </c>
+      <c r="AD131">
+        <v>6.25</v>
+      </c>
+      <c r="AE131">
+        <v>1.48</v>
+      </c>
+      <c r="AF131">
+        <v>2.37</v>
+      </c>
+      <c r="AG131">
+        <v>2.35</v>
+      </c>
+      <c r="AH131">
+        <v>1.6</v>
+      </c>
+      <c r="AI131">
+        <v>2.05</v>
+      </c>
+      <c r="AJ131">
+        <v>1.7</v>
+      </c>
+      <c r="AK131">
+        <v>1.4</v>
+      </c>
+      <c r="AL131">
+        <v>1.33</v>
+      </c>
+      <c r="AM131">
+        <v>1.45</v>
+      </c>
+      <c r="AN131">
+        <v>1.9</v>
+      </c>
+      <c r="AO131">
+        <v>2</v>
+      </c>
+      <c r="AP131">
+        <v>1.73</v>
+      </c>
+      <c r="AQ131">
+        <v>2.14</v>
+      </c>
+      <c r="AR131">
+        <v>1.71</v>
+      </c>
+      <c r="AS131">
+        <v>1.52</v>
+      </c>
+      <c r="AT131">
+        <v>3.23</v>
+      </c>
+      <c r="AU131">
+        <v>5</v>
+      </c>
+      <c r="AV131">
+        <v>3</v>
+      </c>
+      <c r="AW131">
+        <v>4</v>
+      </c>
+      <c r="AX131">
+        <v>11</v>
+      </c>
+      <c r="AY131">
+        <v>9</v>
+      </c>
+      <c r="AZ131">
+        <v>14</v>
+      </c>
+      <c r="BA131">
+        <v>3</v>
+      </c>
+      <c r="BB131">
+        <v>5</v>
+      </c>
+      <c r="BC131">
+        <v>8</v>
+      </c>
+      <c r="BD131">
+        <v>1.73</v>
+      </c>
+      <c r="BE131">
+        <v>8</v>
+      </c>
+      <c r="BF131">
+        <v>2.38</v>
+      </c>
+      <c r="BG131">
+        <v>1.32</v>
+      </c>
+      <c r="BH131">
+        <v>2.88</v>
+      </c>
+      <c r="BI131">
+        <v>1.61</v>
+      </c>
+      <c r="BJ131">
+        <v>2.12</v>
+      </c>
+      <c r="BK131">
+        <v>2.05</v>
+      </c>
+      <c r="BL131">
+        <v>1.7</v>
+      </c>
+      <c r="BM131">
+        <v>2.71</v>
+      </c>
+      <c r="BN131">
+        <v>1.38</v>
+      </c>
+      <c r="BO131">
+        <v>3.76</v>
+      </c>
+      <c r="BP131">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="132" spans="1:68">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132">
+        <v>7919111</v>
+      </c>
+      <c r="C132" t="s">
+        <v>68</v>
+      </c>
+      <c r="D132" t="s">
+        <v>69</v>
+      </c>
+      <c r="E132" s="2">
+        <v>45882.89583333334</v>
+      </c>
+      <c r="F132">
+        <v>0</v>
+      </c>
+      <c r="G132" t="s">
+        <v>109</v>
+      </c>
+      <c r="H132" t="s">
+        <v>114</v>
+      </c>
+      <c r="I132">
+        <v>1</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132">
+        <v>1</v>
+      </c>
+      <c r="L132">
+        <v>1</v>
+      </c>
+      <c r="M132">
+        <v>0</v>
+      </c>
+      <c r="N132">
+        <v>1</v>
+      </c>
+      <c r="O132" t="s">
+        <v>208</v>
+      </c>
+      <c r="P132" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q132">
+        <v>2.05</v>
+      </c>
+      <c r="R132">
+        <v>2.2</v>
+      </c>
+      <c r="S132">
+        <v>7.5</v>
+      </c>
+      <c r="T132">
+        <v>1.44</v>
+      </c>
+      <c r="U132">
+        <v>2.63</v>
+      </c>
+      <c r="V132">
+        <v>3.25</v>
+      </c>
+      <c r="W132">
+        <v>1.33</v>
+      </c>
+      <c r="X132">
+        <v>10</v>
+      </c>
+      <c r="Y132">
+        <v>1.06</v>
+      </c>
+      <c r="Z132">
+        <v>1.44</v>
+      </c>
+      <c r="AA132">
+        <v>3.66</v>
+      </c>
+      <c r="AB132">
+        <v>6.6</v>
+      </c>
+      <c r="AC132">
+        <v>1.07</v>
+      </c>
+      <c r="AD132">
+        <v>8</v>
+      </c>
+      <c r="AE132">
+        <v>1.42</v>
+      </c>
+      <c r="AF132">
+        <v>2.8</v>
+      </c>
+      <c r="AG132">
+        <v>2.3</v>
+      </c>
+      <c r="AH132">
+        <v>1.63</v>
+      </c>
+      <c r="AI132">
+        <v>2.38</v>
+      </c>
+      <c r="AJ132">
+        <v>1.53</v>
+      </c>
+      <c r="AK132">
+        <v>1.1</v>
+      </c>
+      <c r="AL132">
+        <v>1.2</v>
+      </c>
+      <c r="AM132">
+        <v>2.5</v>
+      </c>
+      <c r="AN132">
+        <v>1.83</v>
+      </c>
+      <c r="AO132">
+        <v>1.83</v>
+      </c>
+      <c r="AP132">
+        <v>2</v>
+      </c>
+      <c r="AQ132">
+        <v>1.57</v>
+      </c>
+      <c r="AR132">
+        <v>1.44</v>
+      </c>
+      <c r="AS132">
+        <v>1.37</v>
+      </c>
+      <c r="AT132">
+        <v>2.81</v>
+      </c>
+      <c r="AU132">
+        <v>4</v>
+      </c>
+      <c r="AV132">
+        <v>2</v>
+      </c>
+      <c r="AW132">
+        <v>6</v>
+      </c>
+      <c r="AX132">
+        <v>3</v>
+      </c>
+      <c r="AY132">
+        <v>10</v>
+      </c>
+      <c r="AZ132">
+        <v>5</v>
+      </c>
+      <c r="BA132">
+        <v>4</v>
+      </c>
+      <c r="BB132">
+        <v>5</v>
+      </c>
+      <c r="BC132">
+        <v>9</v>
+      </c>
+      <c r="BD132">
+        <v>1.3</v>
+      </c>
+      <c r="BE132">
+        <v>10</v>
+      </c>
+      <c r="BF132">
+        <v>3.9</v>
+      </c>
+      <c r="BG132">
+        <v>1.26</v>
+      </c>
+      <c r="BH132">
+        <v>3.22</v>
+      </c>
+      <c r="BI132">
+        <v>1.5</v>
+      </c>
+      <c r="BJ132">
+        <v>2.35</v>
+      </c>
+      <c r="BK132">
+        <v>1.95</v>
+      </c>
+      <c r="BL132">
+        <v>1.77</v>
+      </c>
+      <c r="BM132">
+        <v>2.42</v>
+      </c>
+      <c r="BN132">
+        <v>1.47</v>
+      </c>
+      <c r="BO132">
+        <v>3.2</v>
+      </c>
+      <c r="BP132">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South America Copa Libertadores_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South America Copa Libertadores_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP132"/>
+  <dimension ref="A1:BP136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3530,7 +3530,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR14" t="n">
         <v>1.46</v>
@@ -5271,7 +5271,7 @@
         <v>2</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.5</v>
@@ -5928,7 +5928,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR25" t="n">
         <v>0.91</v>
@@ -6797,7 +6797,7 @@
         <v>2</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.5</v>
@@ -7454,7 +7454,7 @@
         <v>0.17</v>
       </c>
       <c r="AQ32" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AR32" t="n">
         <v>0</v>
@@ -7669,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ33" t="n">
         <v>1</v>
@@ -8326,7 +8326,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR36" t="n">
         <v>1.41</v>
@@ -9413,10 +9413,10 @@
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ41" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR41" t="n">
         <v>0</v>
@@ -9634,7 +9634,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ42" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AR42" t="n">
         <v>0</v>
@@ -10070,7 +10070,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR44" t="n">
         <v>0</v>
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.67</v>
@@ -11157,7 +11157,7 @@
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ49" t="n">
         <v>0.17</v>
@@ -11593,7 +11593,7 @@
         <v>3</v>
       </c>
       <c r="AP51" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ51" t="n">
         <v>1.67</v>
@@ -11811,7 +11811,7 @@
         <v>2</v>
       </c>
       <c r="AP52" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.1</v>
@@ -12032,7 +12032,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR53" t="n">
         <v>1.19</v>
@@ -13122,7 +13122,7 @@
         <v>3</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR58" t="n">
         <v>0</v>
@@ -13337,7 +13337,7 @@
         <v>0</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AQ59" t="n">
         <v>0</v>
@@ -14645,7 +14645,7 @@
         <v>1.5</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AQ65" t="n">
         <v>2</v>
@@ -15520,7 +15520,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR69" t="n">
         <v>1.1</v>
@@ -16171,7 +16171,7 @@
         <v>2</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AQ72" t="n">
         <v>2.14</v>
@@ -16392,7 +16392,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ73" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR73" t="n">
         <v>1.4</v>
@@ -16607,10 +16607,10 @@
         <v>1.5</v>
       </c>
       <c r="AP74" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ74" t="n">
         <v>2.14</v>
-      </c>
-      <c r="AQ74" t="n">
-        <v>2</v>
       </c>
       <c r="AR74" t="n">
         <v>1.42</v>
@@ -17697,7 +17697,7 @@
         <v>0</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ79" t="n">
         <v>0.67</v>
@@ -18136,7 +18136,7 @@
         <v>0.17</v>
       </c>
       <c r="AQ81" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AR81" t="n">
         <v>0.76</v>
@@ -19226,7 +19226,7 @@
         <v>0</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR86" t="n">
         <v>0.92</v>
@@ -19444,7 +19444,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ87" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AR87" t="n">
         <v>0.99</v>
@@ -19877,7 +19877,7 @@
         <v>3</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ89" t="n">
         <v>3</v>
@@ -20534,7 +20534,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR92" t="n">
         <v>1.82</v>
@@ -20970,7 +20970,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ94" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR94" t="n">
         <v>1.15</v>
@@ -21185,7 +21185,7 @@
         <v>1.33</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ95" t="n">
         <v>1.33</v>
@@ -21842,7 +21842,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR98" t="n">
         <v>0.9399999999999999</v>
@@ -22929,10 +22929,10 @@
         <v>2.25</v>
       </c>
       <c r="AP103" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ103" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AR103" t="n">
         <v>1.46</v>
@@ -23150,7 +23150,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR104" t="n">
         <v>1.41</v>
@@ -23583,7 +23583,7 @@
         <v>1.38</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ106" t="n">
         <v>1.1</v>
@@ -24458,7 +24458,7 @@
         <v>2</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR110" t="n">
         <v>1.3</v>
@@ -24673,7 +24673,7 @@
         <v>1.25</v>
       </c>
       <c r="AP111" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.33</v>
@@ -25109,7 +25109,7 @@
         <v>1.36</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AQ113" t="n">
         <v>1.33</v>
@@ -25327,7 +25327,7 @@
         <v>2</v>
       </c>
       <c r="AP114" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.67</v>
@@ -25545,7 +25545,7 @@
         <v>0.2</v>
       </c>
       <c r="AP115" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ115" t="n">
         <v>0.17</v>
@@ -25763,10 +25763,10 @@
         <v>1.4</v>
       </c>
       <c r="AP116" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR116" t="n">
         <v>1.76</v>
@@ -26853,7 +26853,7 @@
         <v>2.2</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AQ121" t="n">
         <v>1.83</v>
@@ -27074,7 +27074,7 @@
         <v>1</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR122" t="n">
         <v>1.77</v>
@@ -29033,10 +29033,10 @@
         <v>2</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ131" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AR131" t="n">
         <v>1.71</v>
@@ -29330,6 +29330,878 @@
       </c>
       <c r="BP132" t="n">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="n">
+        <v>7936910</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>45883.79166666666</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Cerro Porteño</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Estudiantes</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="n">
+        <v>1</v>
+      </c>
+      <c r="N133" t="n">
+        <v>1</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>['90+8']</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R133" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S133" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="T133" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U133" t="n">
+        <v>3</v>
+      </c>
+      <c r="V133" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W133" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X133" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="n">
+        <v>8172521</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>45883.79166666666</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>LDU Quito</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>1</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="n">
+        <v>1</v>
+      </c>
+      <c r="L134" t="n">
+        <v>1</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" t="n">
+        <v>1</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>['1']</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R134" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S134" t="n">
+        <v>8</v>
+      </c>
+      <c r="T134" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U134" t="n">
+        <v>3</v>
+      </c>
+      <c r="V134" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W134" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X134" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="n">
+        <v>7919112</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>45883.89583333334</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R135" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S135" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T135" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U135" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V135" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W135" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X135" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="n">
+        <v>7919113</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>45883.89583333334</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Universitario</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="n">
+        <v>3</v>
+      </c>
+      <c r="K136" t="n">
+        <v>3</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
+        <v>4</v>
+      </c>
+      <c r="N136" t="n">
+        <v>4</v>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>['7', '12', '30', '75']</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R136" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S136" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T136" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U136" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V136" t="n">
+        <v>4</v>
+      </c>
+      <c r="W136" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X136" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South America Copa Libertadores_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South America Copa Libertadores_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP136"/>
+  <dimension ref="A1:BP139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4049,7 +4049,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>7793736</v>
+        <v>7834284</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -4069,197 +4069,197 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Alianza Lima</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
         <v>3</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>['41', '48', '63']</t>
+          <t>['5', '58']</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19']</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>1.47</v>
+        <v>1.87</v>
       </c>
       <c r="R17" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
+        <v>7</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB17" t="n">
         <v>9</v>
       </c>
-      <c r="T17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="U17" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="V17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X17" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>10.67</v>
-      </c>
       <c r="AC17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AD17" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AF17" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AM17" t="n">
-        <v>4.62</v>
+        <v>3.1</v>
       </c>
       <c r="AN17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>1</v>
+        <v>2.33</v>
       </c>
       <c r="AP17" t="n">
         <v>1.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.18</v>
+        <v>1.04</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.82</v>
+        <v>2.87</v>
       </c>
       <c r="AU17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX17" t="n">
         <v>3</v>
       </c>
       <c r="AY17" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BA17" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="BB17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BC17" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="BE17" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BF17" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="BJ17" t="n">
-        <v>2.42</v>
+        <v>2.65</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="BM17" t="n">
-        <v>2.45</v>
+        <v>2.16</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="BP17" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="18">
@@ -4267,7 +4267,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>7834284</v>
+        <v>7793736</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -4287,197 +4287,197 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Alianza Lima</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>3</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>['5', '58']</t>
+          <t>['41', '48', '63']</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>['19']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T18" t="n">
-        <v>1.38</v>
+        <v>1.19</v>
       </c>
       <c r="U18" t="n">
-        <v>2.95</v>
+        <v>4.25</v>
       </c>
       <c r="V18" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="W18" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="X18" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.5</v>
+        <v>6.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>9</v>
+        <v>10.67</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AD18" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AF18" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AM18" t="n">
-        <v>3.1</v>
+        <v>4.62</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO18" t="n">
-        <v>2.33</v>
+        <v>1</v>
       </c>
       <c r="AP18" t="n">
         <v>1.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.33</v>
+        <v>0.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.87</v>
+        <v>3.82</v>
       </c>
       <c r="AU18" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AV18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX18" t="n">
         <v>3</v>
       </c>
       <c r="AY18" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AZ18" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA18" t="n">
         <v>5</v>
       </c>
-      <c r="BA18" t="n">
-        <v>12</v>
-      </c>
       <c r="BB18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BC18" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="BE18" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="BJ18" t="n">
-        <v>2.65</v>
+        <v>2.42</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="BL18" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="BM18" t="n">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="BO18" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="BP18" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="19">
@@ -7887,10 +7887,10 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR34" t="n">
         <v>0</v>
@@ -8977,10 +8977,10 @@
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ39" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR39" t="n">
         <v>0</v>
@@ -9198,7 +9198,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ40" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AR40" t="n">
         <v>0</v>
@@ -9849,7 +9849,7 @@
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ43" t="n">
         <v>1.17</v>
@@ -11375,7 +11375,7 @@
         <v>3</v>
       </c>
       <c r="AP50" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ50" t="n">
         <v>1</v>
@@ -11461,7 +11461,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>7859482</v>
+        <v>7859479</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -11481,197 +11481,197 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3']</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '10']</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="R51" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S51" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="T51" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V51" t="n">
+        <v>3</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X51" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE51" t="n">
         <v>1.33</v>
       </c>
-      <c r="U51" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="V51" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X51" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="AE51" t="n">
+      <c r="AF51" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AL51" t="n">
         <v>1.2</v>
       </c>
-      <c r="AF51" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AM51" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AN51" t="n">
         <v>3</v>
       </c>
       <c r="AO51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.1</v>
+        <v>1.67</v>
       </c>
       <c r="AR51" t="n">
-        <v>0.95</v>
+        <v>1.68</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="AT51" t="n">
-        <v>2.21</v>
+        <v>2.68</v>
       </c>
       <c r="AU51" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW51" t="n">
         <v>6</v>
       </c>
-      <c r="AV51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW51" t="n">
+      <c r="AX51" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY51" t="n">
         <v>10</v>
       </c>
-      <c r="AX51" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>16</v>
-      </c>
       <c r="AZ51" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BA51" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BB51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BC51" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="BD51" t="n">
-        <v>1.19</v>
+        <v>1.48</v>
       </c>
       <c r="BE51" t="n">
-        <v>11.2</v>
+        <v>6.9</v>
       </c>
       <c r="BF51" t="n">
-        <v>6.1</v>
+        <v>3.66</v>
       </c>
       <c r="BG51" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="BH51" t="n">
-        <v>2.88</v>
+        <v>2.57</v>
       </c>
       <c r="BI51" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="BJ51" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="BK51" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="BL51" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="BM51" t="n">
-        <v>2.67</v>
+        <v>3.08</v>
       </c>
       <c r="BN51" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="BO51" t="n">
-        <v>3.68</v>
+        <v>4.2</v>
       </c>
       <c r="BP51" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="52">
@@ -11679,7 +11679,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>7859479</v>
+        <v>7859482</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -11699,197 +11699,197 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>['3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>['7', '10']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="R52" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="T52" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="U52" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X52" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AM52" t="n">
         <v>2.75</v>
-      </c>
-      <c r="V52" t="n">
-        <v>3</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X52" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>2.2</v>
       </c>
       <c r="AN52" t="n">
         <v>3</v>
       </c>
       <c r="AO52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP52" t="n">
-        <v>2.25</v>
+        <v>1.86</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.67</v>
+        <v>1.1</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.68</v>
+        <v>0.95</v>
       </c>
       <c r="AS52" t="n">
-        <v>1</v>
+        <v>1.26</v>
       </c>
       <c r="AT52" t="n">
-        <v>2.68</v>
+        <v>2.21</v>
       </c>
       <c r="AU52" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AV52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AW52" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA52" t="n">
         <v>6</v>
       </c>
-      <c r="AX52" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY52" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ52" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA52" t="n">
-        <v>11</v>
-      </c>
       <c r="BB52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BC52" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="BD52" t="n">
-        <v>1.48</v>
+        <v>1.19</v>
       </c>
       <c r="BE52" t="n">
-        <v>6.9</v>
+        <v>11.2</v>
       </c>
       <c r="BF52" t="n">
-        <v>3.66</v>
+        <v>6.1</v>
       </c>
       <c r="BG52" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="BH52" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="BI52" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="BJ52" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="BK52" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="BL52" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="BM52" t="n">
-        <v>3.08</v>
+        <v>2.67</v>
       </c>
       <c r="BN52" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="BO52" t="n">
-        <v>4.2</v>
+        <v>3.68</v>
       </c>
       <c r="BP52" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="53">
@@ -12115,7 +12115,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>7859490</v>
+        <v>7859493</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -12135,31 +12135,31 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Olimpia</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -12168,164 +12168,164 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>['64']</t>
+          <t>['25', '49', '56', '90+3']</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R54" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S54" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="T54" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V54" t="n">
+        <v>4</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X54" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AE54" t="n">
         <v>1.5</v>
       </c>
-      <c r="U54" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V54" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X54" t="n">
+      <c r="AF54" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU54" t="n">
         <v>10</v>
       </c>
-      <c r="Y54" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AM54" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AN54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO54" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AP54" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ54" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR54" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AT54" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU54" t="n">
+      <c r="AV54" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX54" t="n">
         <v>5</v>
       </c>
-      <c r="AV54" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW54" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX54" t="n">
-        <v>8</v>
-      </c>
       <c r="AY54" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AZ54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA54" t="n">
         <v>6</v>
       </c>
       <c r="BB54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BC54" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BD54" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="BE54" t="n">
-        <v>6.25</v>
+        <v>5.8</v>
       </c>
       <c r="BF54" t="n">
-        <v>2.87</v>
+        <v>2.18</v>
       </c>
       <c r="BG54" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="BH54" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="BI54" t="n">
-        <v>1.62</v>
+        <v>1.96</v>
       </c>
       <c r="BJ54" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="BK54" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="BL54" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="BM54" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="BN54" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="BO54" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BP54" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="55">
@@ -12333,7 +12333,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>7859493</v>
+        <v>7859490</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -12353,31 +12353,31 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Olimpia</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N55" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -12386,164 +12386,164 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>['25', '49', '56', '90+3']</t>
+          <t>['64']</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R55" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="T55" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="U55" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V55" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X55" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AG55" t="n">
         <v>2.2</v>
       </c>
-      <c r="V55" t="n">
-        <v>4</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X55" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y55" t="n">
+      <c r="AH55" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR55" t="n">
         <v>1.04</v>
       </c>
-      <c r="Z55" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>3</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AS55" t="n">
-        <v>1.77</v>
+        <v>2.01</v>
       </c>
       <c r="AT55" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="AU55" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ55" t="n">
         <v>10</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY55" t="n">
-        <v>23</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>11</v>
       </c>
       <c r="BA55" t="n">
         <v>6</v>
       </c>
       <c r="BB55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BC55" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BD55" t="n">
-        <v>1.86</v>
+        <v>1.6</v>
       </c>
       <c r="BE55" t="n">
-        <v>5.8</v>
+        <v>6.25</v>
       </c>
       <c r="BF55" t="n">
-        <v>2.18</v>
+        <v>2.87</v>
       </c>
       <c r="BG55" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="BH55" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="BI55" t="n">
-        <v>1.96</v>
+        <v>1.62</v>
       </c>
       <c r="BJ55" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="BK55" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="BL55" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="BM55" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="BN55" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="BO55" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BP55" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="56">
@@ -13555,7 +13555,7 @@
         <v>1</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ60" t="n">
         <v>1</v>
@@ -13776,7 +13776,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR61" t="n">
         <v>0.89</v>
@@ -13994,7 +13994,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR62" t="n">
         <v>1.01</v>
@@ -14209,7 +14209,7 @@
         <v>1.57</v>
       </c>
       <c r="AP63" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ63" t="n">
         <v>1.33</v>
@@ -14295,7 +14295,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>7859499</v>
+        <v>7859502</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -14315,56 +14315,56 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Alianza Lima</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Talleres Córdoba</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11', '57', '90+5']</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['64', '69']</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="R64" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S64" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="T64" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="U64" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="V64" t="n">
         <v>3.75</v>
@@ -14373,31 +14373,31 @@
         <v>1.25</v>
       </c>
       <c r="X64" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z64" t="n">
-        <v>3.28</v>
+        <v>2.31</v>
       </c>
       <c r="AA64" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="AB64" t="n">
-        <v>2.24</v>
+        <v>3.14</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AD64" t="n">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AF64" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AG64" t="n">
         <v>2.63</v>
@@ -14406,49 +14406,49 @@
         <v>1.49</v>
       </c>
       <c r="AI64" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AJ64" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AK64" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AL64" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AM64" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP64" t="n">
         <v>1.33</v>
       </c>
-      <c r="AN64" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO64" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AP64" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AQ64" t="n">
-        <v>2</v>
+        <v>0.67</v>
       </c>
       <c r="AR64" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AS64" t="n">
-        <v>1.75</v>
+        <v>2.06</v>
       </c>
       <c r="AT64" t="n">
-        <v>3.32</v>
+        <v>3.49</v>
       </c>
       <c r="AU64" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AV64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW64" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AX64" t="n">
         <v>8</v>
@@ -14457,55 +14457,55 @@
         <v>15</v>
       </c>
       <c r="AZ64" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BA64" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC64" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BD64" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="BE64" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="BF64" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="BG64" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="BH64" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="BI64" t="n">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="BJ64" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="BK64" t="n">
-        <v>1.89</v>
+        <v>2.15</v>
       </c>
       <c r="BL64" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="BM64" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="BN64" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="BO64" t="n">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="BP64" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="65">
@@ -14513,7 +14513,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>7859502</v>
+        <v>7859499</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -14533,56 +14533,56 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alianza Lima</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Talleres Córdoba</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>4</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S65" t="n">
         <v>3</v>
       </c>
-      <c r="M65" t="n">
-        <v>2</v>
-      </c>
-      <c r="N65" t="n">
-        <v>5</v>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>['11', '57', '90+5']</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>['64', '69']</t>
-        </is>
-      </c>
-      <c r="Q65" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R65" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="S65" t="n">
-        <v>3.6</v>
-      </c>
       <c r="T65" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="U65" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="V65" t="n">
         <v>3.75</v>
@@ -14591,31 +14591,31 @@
         <v>1.25</v>
       </c>
       <c r="X65" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y65" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AC65" t="n">
         <v>1.04</v>
       </c>
-      <c r="Z65" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AD65" t="n">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AF65" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AG65" t="n">
         <v>2.63</v>
@@ -14624,49 +14624,49 @@
         <v>1.49</v>
       </c>
       <c r="AI65" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AJ65" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AK65" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AL65" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM65" t="n">
         <v>1.33</v>
       </c>
-      <c r="AM65" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AN65" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO65" t="n">
         <v>1.5</v>
       </c>
-      <c r="AO65" t="n">
-        <v>0</v>
-      </c>
       <c r="AP65" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.67</v>
+        <v>2</v>
       </c>
       <c r="AR65" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AS65" t="n">
-        <v>2.06</v>
+        <v>1.75</v>
       </c>
       <c r="AT65" t="n">
-        <v>3.49</v>
+        <v>3.32</v>
       </c>
       <c r="AU65" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AV65" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW65" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AX65" t="n">
         <v>8</v>
@@ -14675,55 +14675,55 @@
         <v>15</v>
       </c>
       <c r="AZ65" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA65" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC65" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BD65" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="BE65" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="BF65" t="n">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="BG65" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="BH65" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="BI65" t="n">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="BJ65" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="BK65" t="n">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="BL65" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="BM65" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="BN65" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="BO65" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="BP65" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="66">
@@ -15084,7 +15084,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR67" t="n">
         <v>1.16</v>
@@ -15603,7 +15603,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>7859510</v>
+        <v>7859509</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -15623,197 +15623,197 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Olimpia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Peñarol</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
         <v>3</v>
       </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>['26', '86']</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>['90']</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>5</v>
-      </c>
       <c r="R70" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="S70" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V70" t="n">
+        <v>4</v>
+      </c>
+      <c r="W70" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X70" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF70" t="n">
         <v>2.3</v>
       </c>
-      <c r="T70" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U70" t="n">
+      <c r="AG70" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AQ70" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AT70" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="AU70" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV70" t="n">
         <v>3</v>
       </c>
-      <c r="V70" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="W70" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X70" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y70" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z70" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA70" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="AB70" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AC70" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD70" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AE70" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF70" t="n">
+      <c r="AW70" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX70" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY70" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ70" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA70" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB70" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC70" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD70" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BE70" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="BF70" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BG70" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BH70" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BI70" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BJ70" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BK70" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BL70" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BM70" t="n">
         <v>3.4</v>
       </c>
-      <c r="AG70" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH70" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AI70" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ70" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AK70" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL70" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AM70" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN70" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO70" t="n">
-        <v>3</v>
-      </c>
-      <c r="AP70" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ70" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AR70" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AS70" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AT70" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AU70" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV70" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW70" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX70" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY70" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ70" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA70" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB70" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC70" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD70" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BE70" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF70" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BG70" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BH70" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BI70" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BJ70" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BK70" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BL70" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BM70" t="n">
-        <v>3.15</v>
-      </c>
       <c r="BN70" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="BO70" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BP70" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="71">
@@ -15821,7 +15821,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>7859509</v>
+        <v>7859510</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -15841,197 +15841,197 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Olimpia</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Peñarol</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['26', '86']</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90']</t>
         </is>
       </c>
       <c r="Q71" t="n">
+        <v>5</v>
+      </c>
+      <c r="R71" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S71" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U71" t="n">
         <v>3</v>
       </c>
-      <c r="R71" t="n">
+      <c r="V71" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W71" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X71" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH71" t="n">
         <v>1.91</v>
       </c>
-      <c r="S71" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T71" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="U71" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V71" t="n">
+      <c r="AI71" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ71" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AR71" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AS71" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AT71" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU71" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV71" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW71" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX71" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY71" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ71" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA71" t="n">
         <v>4</v>
       </c>
-      <c r="W71" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X71" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y71" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z71" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AA71" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AB71" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AC71" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD71" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AE71" t="n">
+      <c r="BB71" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC71" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD71" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BE71" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF71" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BG71" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BH71" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BI71" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BJ71" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BK71" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BL71" t="n">
         <v>1.5</v>
       </c>
-      <c r="AF71" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG71" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AH71" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AI71" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AJ71" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AK71" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AL71" t="n">
+      <c r="BM71" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BN71" t="n">
         <v>1.3</v>
       </c>
-      <c r="AM71" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AN71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO71" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AP71" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AQ71" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR71" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AS71" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AT71" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="AU71" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV71" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW71" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX71" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY71" t="n">
-        <v>20</v>
-      </c>
-      <c r="AZ71" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA71" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB71" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC71" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD71" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BE71" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="BF71" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BG71" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BH71" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BI71" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BJ71" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BK71" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="BL71" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BM71" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BN71" t="n">
-        <v>1.26</v>
-      </c>
       <c r="BO71" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BP71" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="72">
@@ -16039,7 +16039,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>7859495</v>
+        <v>7859501</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -16059,197 +16059,197 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>['38']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['62', '83']</t>
         </is>
       </c>
       <c r="Q72" t="n">
+        <v>4</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S72" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V72" t="n">
+        <v>4</v>
+      </c>
+      <c r="W72" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X72" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN72" t="n">
         <v>3</v>
       </c>
-      <c r="R72" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S72" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T72" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="U72" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V72" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="W72" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X72" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y72" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z72" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AA72" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AB72" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AC72" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AD72" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AE72" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF72" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG72" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AH72" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AI72" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ72" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AK72" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AL72" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AM72" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AN72" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AO72" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AP72" t="n">
-        <v>2.25</v>
+        <v>1.43</v>
       </c>
       <c r="AQ72" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AR72" t="n">
-        <v>1.42</v>
+        <v>1.07</v>
       </c>
       <c r="AS72" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AT72" t="n">
-        <v>3.12</v>
+        <v>2.84</v>
       </c>
       <c r="AU72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV72" t="n">
         <v>4</v>
       </c>
       <c r="AW72" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX72" t="n">
         <v>4</v>
       </c>
       <c r="AY72" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ72" t="n">
         <v>8</v>
       </c>
       <c r="BA72" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BB72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC72" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BD72" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="BE72" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="BF72" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="BG72" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="BH72" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="BI72" t="n">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="BJ72" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="BK72" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="BL72" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BM72" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="BN72" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="BO72" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BP72" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="73">
@@ -16475,7 +16475,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>7859501</v>
+        <v>7859495</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -16495,197 +16495,197 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
+          <t>['38']</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>['62', '83']</t>
-        </is>
-      </c>
       <c r="Q74" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R74" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="S74" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="T74" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="U74" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="V74" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="W74" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X74" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y74" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AC74" t="n">
         <v>1.04</v>
       </c>
-      <c r="Z74" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA74" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AB74" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AC74" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AD74" t="n">
-        <v>5.55</v>
+        <v>7.4</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AF74" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AG74" t="n">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="AH74" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AI74" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AJ74" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AK74" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AL74" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AM74" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AN74" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO74" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.43</v>
+        <v>2.25</v>
       </c>
       <c r="AQ74" t="n">
         <v>2.14</v>
       </c>
       <c r="AR74" t="n">
-        <v>1.07</v>
+        <v>1.42</v>
       </c>
       <c r="AS74" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AT74" t="n">
-        <v>2.84</v>
+        <v>3.12</v>
       </c>
       <c r="AU74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV74" t="n">
         <v>4</v>
       </c>
       <c r="AW74" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX74" t="n">
         <v>4</v>
       </c>
       <c r="AY74" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AZ74" t="n">
         <v>8</v>
       </c>
       <c r="BA74" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BB74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC74" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="BD74" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="BE74" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="BF74" t="n">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="BG74" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="BH74" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="BI74" t="n">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="BJ74" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="BK74" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="BL74" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="BM74" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="BN74" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="BO74" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BP74" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="75">
@@ -16828,7 +16828,7 @@
         <v>1</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR75" t="n">
         <v>1.54</v>
@@ -16911,7 +16911,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>7859507</v>
+        <v>7859500</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -16931,50 +16931,50 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Central Córdoba SdE</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Deportivo Táchira</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L76" t="n">
         <v>2</v>
       </c>
       <c r="M76" t="n">
+        <v>1</v>
+      </c>
+      <c r="N76" t="n">
         <v>3</v>
       </c>
-      <c r="N76" t="n">
-        <v>5</v>
-      </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>['56', '69']</t>
+          <t>['4', '19']</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>['19', '45', '73']</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="R76" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S76" t="n">
-        <v>4.5</v>
+        <v>9.5</v>
       </c>
       <c r="T76" t="n">
         <v>1.44</v>
@@ -16983,10 +16983,10 @@
         <v>2.63</v>
       </c>
       <c r="V76" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="W76" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="X76" t="n">
         <v>9</v>
@@ -16995,133 +16995,133 @@
         <v>1.07</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.94</v>
+        <v>1.34</v>
       </c>
       <c r="AA76" t="n">
-        <v>3.32</v>
+        <v>4.6</v>
       </c>
       <c r="AB76" t="n">
-        <v>3.93</v>
+        <v>9.4</v>
       </c>
       <c r="AC76" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AD76" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AF76" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="AG76" t="n">
-        <v>1.95</v>
+        <v>2.37</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.79</v>
+        <v>1.48</v>
       </c>
       <c r="AI76" t="n">
-        <v>1.91</v>
+        <v>2.63</v>
       </c>
       <c r="AJ76" t="n">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="AK76" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AL76" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AM76" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP76" t="n">
         <v>1.83</v>
       </c>
-      <c r="AN76" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO76" t="n">
-        <v>3</v>
-      </c>
-      <c r="AP76" t="n">
-        <v>1</v>
-      </c>
       <c r="AQ76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AR76" t="n">
-        <v>2.13</v>
+        <v>1.43</v>
       </c>
       <c r="AS76" t="n">
-        <v>2.05</v>
+        <v>0.86</v>
       </c>
       <c r="AT76" t="n">
-        <v>4.18</v>
+        <v>2.29</v>
       </c>
       <c r="AU76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX76" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY76" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ76" t="n">
         <v>9</v>
       </c>
-      <c r="AW76" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX76" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY76" t="n">
-        <v>19</v>
-      </c>
-      <c r="AZ76" t="n">
-        <v>12</v>
-      </c>
       <c r="BA76" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="BB76" t="n">
         <v>3</v>
       </c>
       <c r="BC76" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="BD76" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="BE76" t="n">
-        <v>9.5</v>
+        <v>8.9</v>
       </c>
       <c r="BF76" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BG76" t="n">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="BH76" t="n">
-        <v>5.3</v>
+        <v>2.05</v>
       </c>
       <c r="BI76" t="n">
-        <v>1.21</v>
+        <v>2.05</v>
       </c>
       <c r="BJ76" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="BK76" t="n">
-        <v>1.36</v>
+        <v>2.92</v>
       </c>
       <c r="BL76" t="n">
-        <v>2.8</v>
+        <v>1.31</v>
       </c>
       <c r="BM76" t="n">
-        <v>1.57</v>
+        <v>3.3</v>
       </c>
       <c r="BN76" t="n">
-        <v>2.23</v>
+        <v>1.28</v>
       </c>
       <c r="BO76" t="n">
-        <v>1.88</v>
+        <v>4.4</v>
       </c>
       <c r="BP76" t="n">
-        <v>1.81</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="77">
@@ -17129,7 +17129,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>7859500</v>
+        <v>7859507</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -17149,50 +17149,50 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Central Córdoba SdE</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Deportivo Táchira</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K77" t="n">
+        <v>2</v>
+      </c>
+      <c r="L77" t="n">
+        <v>2</v>
+      </c>
+      <c r="M77" t="n">
         <v>3</v>
       </c>
-      <c r="L77" t="n">
-        <v>2</v>
-      </c>
-      <c r="M77" t="n">
-        <v>1</v>
-      </c>
       <c r="N77" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>['4', '19']</t>
+          <t>['56', '69']</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>['37']</t>
+          <t>['19', '45', '73']</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="R77" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S77" t="n">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
       <c r="T77" t="n">
         <v>1.44</v>
@@ -17201,10 +17201,10 @@
         <v>2.63</v>
       </c>
       <c r="V77" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="W77" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="X77" t="n">
         <v>9</v>
@@ -17213,133 +17213,133 @@
         <v>1.07</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.34</v>
+        <v>1.94</v>
       </c>
       <c r="AA77" t="n">
-        <v>4.6</v>
+        <v>3.32</v>
       </c>
       <c r="AB77" t="n">
-        <v>9.4</v>
+        <v>3.93</v>
       </c>
       <c r="AC77" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AD77" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AF77" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="AG77" t="n">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="AI77" t="n">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="AJ77" t="n">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AK77" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AL77" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AM77" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO77" t="n">
         <v>3</v>
       </c>
-      <c r="AN77" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO77" t="n">
-        <v>0</v>
-      </c>
       <c r="AP77" t="n">
-        <v>1.83</v>
+        <v>1</v>
       </c>
       <c r="AQ77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AR77" t="n">
-        <v>1.43</v>
+        <v>2.13</v>
       </c>
       <c r="AS77" t="n">
-        <v>0.86</v>
+        <v>2.05</v>
       </c>
       <c r="AT77" t="n">
-        <v>2.29</v>
+        <v>4.18</v>
       </c>
       <c r="AU77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV77" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AW77" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AX77" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AY77" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AZ77" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA77" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="BB77" t="n">
         <v>3</v>
       </c>
       <c r="BC77" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="BD77" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="BE77" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="BF77" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BG77" t="n">
-        <v>1.7</v>
+        <v>1.11</v>
       </c>
       <c r="BH77" t="n">
-        <v>2.05</v>
+        <v>5.3</v>
       </c>
       <c r="BI77" t="n">
-        <v>2.05</v>
+        <v>1.21</v>
       </c>
       <c r="BJ77" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="BK77" t="n">
-        <v>2.92</v>
+        <v>1.36</v>
       </c>
       <c r="BL77" t="n">
-        <v>1.31</v>
+        <v>2.8</v>
       </c>
       <c r="BM77" t="n">
-        <v>3.3</v>
+        <v>1.57</v>
       </c>
       <c r="BN77" t="n">
-        <v>1.28</v>
+        <v>2.23</v>
       </c>
       <c r="BO77" t="n">
-        <v>4.4</v>
+        <v>1.88</v>
       </c>
       <c r="BP77" t="n">
-        <v>1.15</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="78">
@@ -17482,7 +17482,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR78" t="n">
         <v>1.85</v>
@@ -17783,7 +17783,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>7859520</v>
+        <v>7859518</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -17803,12 +17803,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga</t>
+          <t>Alianza Lima</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -17824,10 +17824,10 @@
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N80" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -17836,62 +17836,62 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>['4', '56', '69', '90+4']</t>
+          <t>['35', '89']</t>
         </is>
       </c>
       <c r="Q80" t="n">
         <v>4</v>
       </c>
       <c r="R80" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S80" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T80" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="U80" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V80" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="W80" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X80" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z80" t="n">
-        <v>3.07</v>
+        <v>3.17</v>
       </c>
       <c r="AA80" t="n">
-        <v>3.02</v>
+        <v>2.92</v>
       </c>
       <c r="AB80" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AC80" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AD80" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AF80" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AG80" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AI80" t="n">
         <v>2</v>
@@ -17900,46 +17900,46 @@
         <v>1.75</v>
       </c>
       <c r="AK80" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AL80" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AM80" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AN80" t="n">
         <v>1.67</v>
       </c>
       <c r="AO80" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AP80" t="n">
         <v>1.33</v>
       </c>
-      <c r="AP80" t="n">
-        <v>1</v>
-      </c>
       <c r="AQ80" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR80" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="AS80" t="n">
-        <v>1.96</v>
+        <v>1.48</v>
       </c>
       <c r="AT80" t="n">
-        <v>3.56</v>
+        <v>2.94</v>
       </c>
       <c r="AU80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV80" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW80" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX80" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY80" t="n">
         <v>11</v>
@@ -17948,52 +17948,52 @@
         <v>11</v>
       </c>
       <c r="BA80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB80" t="n">
         <v>3</v>
       </c>
       <c r="BC80" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD80" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="BE80" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="BF80" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="BG80" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="BH80" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="BI80" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="BJ80" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="BK80" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="BL80" t="n">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="BM80" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="BN80" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="BO80" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="BP80" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="81">
@@ -18219,7 +18219,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>7859518</v>
+        <v>7859520</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -18239,12 +18239,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alianza Lima</t>
+          <t>Atlético Bucaramanga</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="I82" t="n">
@@ -18260,10 +18260,10 @@
         <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -18272,62 +18272,62 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>['35', '89']</t>
+          <t>['4', '56', '69', '90+4']</t>
         </is>
       </c>
       <c r="Q82" t="n">
         <v>4</v>
       </c>
       <c r="R82" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S82" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T82" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U82" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V82" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W82" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X82" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH82" t="n">
         <v>1.53</v>
-      </c>
-      <c r="U82" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V82" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="W82" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X82" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y82" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z82" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="AA82" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AB82" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AC82" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD82" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AE82" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AF82" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AG82" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AH82" t="n">
-        <v>1.48</v>
       </c>
       <c r="AI82" t="n">
         <v>2</v>
@@ -18336,46 +18336,46 @@
         <v>1.75</v>
       </c>
       <c r="AK82" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AL82" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AM82" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AN82" t="n">
         <v>1.67</v>
       </c>
       <c r="AO82" t="n">
-        <v>2.33</v>
+        <v>1.33</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ82" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AR82" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="AS82" t="n">
-        <v>1.48</v>
+        <v>1.96</v>
       </c>
       <c r="AT82" t="n">
-        <v>2.94</v>
+        <v>3.56</v>
       </c>
       <c r="AU82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV82" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW82" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX82" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY82" t="n">
         <v>11</v>
@@ -18384,52 +18384,52 @@
         <v>11</v>
       </c>
       <c r="BA82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB82" t="n">
         <v>3</v>
       </c>
       <c r="BC82" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD82" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="BE82" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="BF82" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="BG82" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="BH82" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="BI82" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="BJ82" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="BK82" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="BL82" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="BM82" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="BN82" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="BO82" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="BP82" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="83">
@@ -18569,7 +18569,7 @@
         <v>0.67</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ83" t="n">
         <v>0.83</v>
@@ -18790,7 +18790,7 @@
         <v>1</v>
       </c>
       <c r="AQ84" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR84" t="n">
         <v>1.12</v>
@@ -19527,7 +19527,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>7859516</v>
+        <v>7859524</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -19547,12 +19547,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Central Córdoba SdE</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="I88" t="n">
@@ -19565,32 +19565,32 @@
         <v>1</v>
       </c>
       <c r="L88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N88" t="n">
         <v>2</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>['61']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>['10']</t>
+          <t>['41', '90+4']</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R88" t="n">
         <v>2.1</v>
       </c>
       <c r="S88" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="T88" t="n">
         <v>1.44</v>
@@ -19605,109 +19605,109 @@
         <v>1.33</v>
       </c>
       <c r="X88" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z88" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA88" t="n">
-        <v>3.45</v>
+        <v>3.07</v>
       </c>
       <c r="AB88" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH88" t="n">
         <v>1.57</v>
       </c>
-      <c r="AC88" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AD88" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE88" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF88" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AG88" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH88" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AI88" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AJ88" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AK88" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AL88" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM88" t="n">
         <v>1.22</v>
       </c>
-      <c r="AM88" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AN88" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AO88" t="n">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="AQ88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR88" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AS88" t="n">
-        <v>1.52</v>
+        <v>1.82</v>
       </c>
       <c r="AT88" t="n">
-        <v>3.18</v>
+        <v>3.62</v>
       </c>
       <c r="AU88" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV88" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AW88" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AX88" t="n">
         <v>3</v>
       </c>
       <c r="AY88" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ88" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA88" t="n">
         <v>8</v>
       </c>
-      <c r="AZ88" t="n">
+      <c r="BB88" t="n">
         <v>5</v>
       </c>
-      <c r="BA88" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB88" t="n">
-        <v>1</v>
-      </c>
       <c r="BC88" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="BD88" t="n">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="BE88" t="n">
-        <v>6.75</v>
+        <v>6.4</v>
       </c>
       <c r="BF88" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="BG88" t="n">
         <v>1.48</v>
@@ -19725,19 +19725,19 @@
         <v>2.3</v>
       </c>
       <c r="BL88" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="BM88" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="BN88" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO88" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP88" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="89">
@@ -19745,7 +19745,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>7859524</v>
+        <v>7859516</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -19765,12 +19765,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Central Córdoba SdE</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="I89" t="n">
@@ -19783,32 +19783,32 @@
         <v>1</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N89" t="n">
         <v>2</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>['41', '90+4']</t>
+          <t>['10']</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R89" t="n">
         <v>2.1</v>
       </c>
       <c r="S89" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="T89" t="n">
         <v>1.44</v>
@@ -19823,109 +19823,109 @@
         <v>1.33</v>
       </c>
       <c r="X89" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y89" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z89" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AA89" t="n">
-        <v>3.07</v>
+        <v>3.45</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AC89" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AD89" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AF89" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AG89" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH89" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AI89" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AJ89" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AK89" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AL89" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AM89" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AN89" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AO89" t="n">
-        <v>3</v>
+        <v>1.33</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="AQ89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR89" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AS89" t="n">
-        <v>1.82</v>
+        <v>1.52</v>
       </c>
       <c r="AT89" t="n">
-        <v>3.62</v>
+        <v>3.18</v>
       </c>
       <c r="AU89" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV89" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AW89" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AX89" t="n">
         <v>3</v>
       </c>
       <c r="AY89" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AZ89" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BA89" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="BB89" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BC89" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="BD89" t="n">
-        <v>2.65</v>
+        <v>3.05</v>
       </c>
       <c r="BE89" t="n">
-        <v>6.4</v>
+        <v>6.75</v>
       </c>
       <c r="BF89" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="BG89" t="n">
         <v>1.48</v>
@@ -19943,19 +19943,19 @@
         <v>2.3</v>
       </c>
       <c r="BL89" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="BM89" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="BN89" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="BO89" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP89" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="90">
@@ -20313,7 +20313,7 @@
         <v>0.33</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ91" t="n">
         <v>0.83</v>
@@ -20617,7 +20617,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>7859514</v>
+        <v>7859521</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -20637,50 +20637,50 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Atlético Nacional</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="I93" t="n">
         <v>1</v>
       </c>
       <c r="J93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
+        <v>1</v>
+      </c>
+      <c r="L93" t="n">
         <v>3</v>
       </c>
-      <c r="L93" t="n">
-        <v>2</v>
-      </c>
       <c r="M93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N93" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>['15', '49']</t>
+          <t>['39', '55', '90+3']</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>['7', '26', '48']</t>
+          <t>['80']</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>4.75</v>
+        <v>3.1</v>
       </c>
       <c r="R93" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S93" t="n">
-        <v>2.6</v>
+        <v>3.75</v>
       </c>
       <c r="T93" t="n">
         <v>1.44</v>
@@ -20701,13 +20701,13 @@
         <v>1.07</v>
       </c>
       <c r="Z93" t="n">
-        <v>3.59</v>
+        <v>2.2</v>
       </c>
       <c r="AA93" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.9</v>
+        <v>2.86</v>
       </c>
       <c r="AC93" t="n">
         <v>1.07</v>
@@ -20719,115 +20719,115 @@
         <v>1.4</v>
       </c>
       <c r="AF93" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AG93" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH93" t="n">
         <v>1.61</v>
       </c>
       <c r="AI93" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AJ93" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AK93" t="n">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="AL93" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AM93" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="AN93" t="n">
-        <v>1.57</v>
+        <v>1</v>
       </c>
       <c r="AO93" t="n">
         <v>1.67</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.1</v>
+        <v>1.38</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="AR93" t="n">
-        <v>1.15</v>
+        <v>1.65</v>
       </c>
       <c r="AS93" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="AT93" t="n">
-        <v>2.69</v>
+        <v>2.98</v>
       </c>
       <c r="AU93" t="n">
         <v>3</v>
       </c>
       <c r="AV93" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AW93" t="n">
         <v>8</v>
       </c>
       <c r="AX93" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY93" t="n">
         <v>11</v>
       </c>
       <c r="AZ93" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA93" t="n">
         <v>3</v>
       </c>
       <c r="BB93" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BC93" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BD93" t="n">
-        <v>2.45</v>
+        <v>1.65</v>
       </c>
       <c r="BE93" t="n">
         <v>8.5</v>
       </c>
       <c r="BF93" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="BG93" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="BH93" t="n">
-        <v>2.78</v>
+        <v>3.04</v>
       </c>
       <c r="BI93" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BJ93" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BK93" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BL93" t="n">
         <v>1.7</v>
       </c>
-      <c r="BJ93" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BK93" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BL93" t="n">
-        <v>1.6</v>
-      </c>
       <c r="BM93" t="n">
-        <v>2.83</v>
+        <v>2.6</v>
       </c>
       <c r="BN93" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="BO93" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BP93" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="94">
@@ -20835,7 +20835,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>7859521</v>
+        <v>7859514</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -20855,50 +20855,50 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="I94" t="n">
         <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L94" t="n">
+        <v>2</v>
+      </c>
+      <c r="M94" t="n">
         <v>3</v>
       </c>
-      <c r="M94" t="n">
-        <v>1</v>
-      </c>
       <c r="N94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>['39', '55', '90+3']</t>
+          <t>['15', '49']</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>['80']</t>
+          <t>['7', '26', '48']</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="R94" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S94" t="n">
-        <v>3.75</v>
+        <v>2.6</v>
       </c>
       <c r="T94" t="n">
         <v>1.44</v>
@@ -20919,13 +20919,13 @@
         <v>1.07</v>
       </c>
       <c r="Z94" t="n">
-        <v>2.2</v>
+        <v>3.59</v>
       </c>
       <c r="AA94" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="AB94" t="n">
-        <v>2.86</v>
+        <v>1.9</v>
       </c>
       <c r="AC94" t="n">
         <v>1.07</v>
@@ -20937,115 +20937,115 @@
         <v>1.4</v>
       </c>
       <c r="AF94" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AG94" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH94" t="n">
         <v>1.61</v>
       </c>
       <c r="AI94" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AJ94" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AK94" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="AL94" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AM94" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AN94" t="n">
-        <v>1</v>
+        <v>1.57</v>
       </c>
       <c r="AO94" t="n">
         <v>1.67</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.43</v>
+        <v>1.1</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
       <c r="AR94" t="n">
-        <v>1.65</v>
+        <v>1.15</v>
       </c>
       <c r="AS94" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="AT94" t="n">
-        <v>2.98</v>
+        <v>2.69</v>
       </c>
       <c r="AU94" t="n">
         <v>3</v>
       </c>
       <c r="AV94" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AW94" t="n">
         <v>8</v>
       </c>
       <c r="AX94" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY94" t="n">
         <v>11</v>
       </c>
       <c r="AZ94" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BA94" t="n">
         <v>3</v>
       </c>
       <c r="BB94" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC94" t="n">
         <v>7</v>
       </c>
-      <c r="BC94" t="n">
-        <v>10</v>
-      </c>
       <c r="BD94" t="n">
-        <v>1.65</v>
+        <v>2.45</v>
       </c>
       <c r="BE94" t="n">
         <v>8.5</v>
       </c>
       <c r="BF94" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="BG94" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="BH94" t="n">
-        <v>3.04</v>
+        <v>2.78</v>
       </c>
       <c r="BI94" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="BJ94" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="BK94" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="BL94" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="BM94" t="n">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="BN94" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="BO94" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BP94" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="95">
@@ -21621,7 +21621,7 @@
         <v>1.25</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ97" t="n">
         <v>1</v>
@@ -22143,7 +22143,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>7859542</v>
+        <v>7859541</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -22163,197 +22163,197 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Peñarol</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Olimpia</t>
         </is>
       </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L100" t="n">
         <v>3</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N100" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>['68', '79', '90+3']</t>
+          <t>['50', '55', '73']</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13', '37']</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>1.44</v>
+        <v>2.5</v>
       </c>
       <c r="R100" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T100" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U100" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V100" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W100" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X100" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD100" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK100" t="n">
         <v>1.22</v>
       </c>
-      <c r="U100" t="n">
-        <v>4</v>
-      </c>
-      <c r="V100" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="W100" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="X100" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y100" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z100" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AA100" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AB100" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC100" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD100" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE100" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF100" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AG100" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH100" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AI100" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AJ100" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AK100" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AL100" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AM100" t="n">
-        <v>5.25</v>
+        <v>1.9</v>
       </c>
       <c r="AN100" t="n">
         <v>1.75</v>
       </c>
       <c r="AO100" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AR100" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="AS100" t="n">
-        <v>0.95</v>
+        <v>1.99</v>
       </c>
       <c r="AT100" t="n">
-        <v>2.53</v>
+        <v>3.39</v>
       </c>
       <c r="AU100" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV100" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW100" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX100" t="n">
         <v>8</v>
       </c>
-      <c r="AV100" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW100" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX100" t="n">
-        <v>3</v>
-      </c>
       <c r="AY100" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AZ100" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="BA100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC100" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BD100" t="n">
-        <v>1.08</v>
+        <v>1.42</v>
       </c>
       <c r="BE100" t="n">
-        <v>11.5</v>
+        <v>6.75</v>
       </c>
       <c r="BF100" t="n">
-        <v>8</v>
+        <v>3.3</v>
       </c>
       <c r="BG100" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="BH100" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="BI100" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="BJ100" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="BK100" t="n">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="BL100" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="BM100" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="BN100" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="BO100" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="BP100" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="101">
@@ -22361,7 +22361,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>7859538</v>
+        <v>7859542</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -22381,12 +22381,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="I101" t="n">
@@ -22399,17 +22399,17 @@
         <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>['46']</t>
+          <t>['68', '79', '90+3']</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -22418,160 +22418,160 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>2.65</v>
+        <v>1.44</v>
       </c>
       <c r="R101" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S101" t="n">
+        <v>15</v>
+      </c>
+      <c r="T101" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U101" t="n">
+        <v>4</v>
+      </c>
+      <c r="V101" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W101" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X101" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC101" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AI101" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ101" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AK101" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AL101" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AM101" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO101" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP101" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AQ101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR101" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS101" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AT101" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AU101" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW101" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX101" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY101" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ101" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA101" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC101" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD101" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BE101" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF101" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG101" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BH101" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BI101" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BJ101" t="n">
         <v>2.08</v>
       </c>
-      <c r="S101" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T101" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="U101" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="V101" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="W101" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X101" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y101" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z101" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AA101" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AB101" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AC101" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AD101" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE101" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF101" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AG101" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH101" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI101" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AJ101" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AK101" t="n">
+      <c r="BK101" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BL101" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BM101" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BN101" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BO101" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP101" t="n">
         <v>1.27</v>
-      </c>
-      <c r="AL101" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AM101" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AN101" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO101" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AP101" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AQ101" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR101" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AS101" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AT101" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU101" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV101" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW101" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX101" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY101" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ101" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA101" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB101" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC101" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD101" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BE101" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="BF101" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BG101" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BH101" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI101" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BJ101" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BK101" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BL101" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BM101" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BN101" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BO101" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BP101" t="n">
-        <v>1.33</v>
       </c>
     </row>
     <row r="102">
@@ -22579,7 +22579,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>7859541</v>
+        <v>7859538</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -22599,197 +22599,197 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Peñarol</t>
+          <t>Atlético Nacional</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Olimpia</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="I102" t="n">
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L102" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>['50', '55', '73']</t>
+          <t>['46']</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>['13', '37']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="R102" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="T102" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="U102" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="V102" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="W102" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="X102" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y102" t="n">
         <v>1.06</v>
       </c>
       <c r="Z102" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC102" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD102" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH102" t="n">
         <v>1.67</v>
       </c>
-      <c r="AA102" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="AB102" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AC102" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AD102" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE102" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF102" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AG102" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH102" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AI102" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AJ102" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AK102" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AL102" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AM102" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AN102" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AO102" t="n">
-        <v>0.5</v>
+        <v>1.88</v>
       </c>
       <c r="AP102" t="n">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="AQ102" t="n">
-        <v>0.83</v>
+        <v>1.5</v>
       </c>
       <c r="AR102" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AS102" t="n">
-        <v>1.99</v>
+        <v>1.79</v>
       </c>
       <c r="AT102" t="n">
-        <v>3.39</v>
+        <v>3.3</v>
       </c>
       <c r="AU102" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW102" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX102" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY102" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ102" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA102" t="n">
         <v>7</v>
       </c>
-      <c r="AV102" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW102" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX102" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY102" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ102" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA102" t="n">
-        <v>5</v>
-      </c>
       <c r="BB102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC102" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BD102" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="BE102" t="n">
         <v>6.75</v>
       </c>
       <c r="BF102" t="n">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="BG102" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="BH102" t="n">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="BI102" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="BJ102" t="n">
-        <v>1.98</v>
+        <v>2.35</v>
       </c>
       <c r="BK102" t="n">
-        <v>2.17</v>
+        <v>1.83</v>
       </c>
       <c r="BL102" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="BM102" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="BN102" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="BO102" t="n">
-        <v>3.65</v>
+        <v>2.95</v>
       </c>
       <c r="BP102" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="103">
@@ -22929,7 +22929,7 @@
         <v>0.5</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ103" t="n">
         <v>0.83</v>
@@ -23365,7 +23365,7 @@
         <v>1.75</v>
       </c>
       <c r="AP105" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ105" t="n">
         <v>1.43</v>
@@ -24891,7 +24891,7 @@
         <v>0.8</v>
       </c>
       <c r="AP112" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ112" t="n">
         <v>0.67</v>
@@ -26202,7 +26202,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR118" t="n">
         <v>1.36</v>
@@ -26503,7 +26503,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="n">
-        <v>7859547</v>
+        <v>7859556</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -26523,35 +26523,35 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Deportivo Táchira</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L120" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M120" t="n">
         <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>['66']</t>
+          <t>['41', '4502', '50', '80']</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -26560,160 +26560,160 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>1.3</v>
+        <v>1.83</v>
       </c>
       <c r="R120" t="n">
-        <v>3.75</v>
+        <v>2.6</v>
       </c>
       <c r="S120" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="T120" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U120" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V120" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W120" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X120" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AL120" t="n">
         <v>1.17</v>
       </c>
-      <c r="U120" t="n">
-        <v>5</v>
-      </c>
-      <c r="V120" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W120" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="X120" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y120" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z120" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AA120" t="n">
-        <v>12</v>
-      </c>
-      <c r="AB120" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC120" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD120" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE120" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF120" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AG120" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH120" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="AI120" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AJ120" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AK120" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL120" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AM120" t="n">
-        <v>10</v>
+        <v>2.95</v>
       </c>
       <c r="AN120" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="AO120" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AP120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ120" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR120" t="n">
-        <v>1.44</v>
+        <v>1.77</v>
       </c>
       <c r="AS120" t="n">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="AT120" t="n">
-        <v>2.88</v>
+        <v>3.48</v>
       </c>
       <c r="AU120" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW120" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AX120" t="n">
         <v>4</v>
       </c>
       <c r="AY120" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AZ120" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA120" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB120" t="n">
         <v>4</v>
       </c>
-      <c r="BB120" t="n">
-        <v>2</v>
-      </c>
       <c r="BC120" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BD120" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="BE120" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="BF120" t="n">
-        <v>7.5</v>
+        <v>5.4</v>
       </c>
       <c r="BG120" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="BH120" t="n">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="BI120" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="BJ120" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="BK120" t="n">
-        <v>1.47</v>
+        <v>1.68</v>
       </c>
       <c r="BL120" t="n">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="BM120" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="BN120" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="BO120" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="BP120" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="121">
@@ -26939,7 +26939,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="n">
-        <v>7859556</v>
+        <v>7859548</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -26959,12 +26959,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Central Córdoba SdE</t>
         </is>
       </c>
       <c r="I122" t="n">
@@ -26977,179 +26977,179 @@
         <v>2</v>
       </c>
       <c r="L122" t="n">
+        <v>3</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="n">
+        <v>3</v>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>['15', '44', '53']</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R122" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S122" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T122" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U122" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V122" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W122" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X122" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AU122" t="n">
         <v>4</v>
       </c>
-      <c r="M122" t="n">
-        <v>0</v>
-      </c>
-      <c r="N122" t="n">
+      <c r="AV122" t="n">
         <v>4</v>
       </c>
-      <c r="O122" t="inlineStr">
-        <is>
-          <t>['41', '4502', '50', '80']</t>
-        </is>
-      </c>
-      <c r="P122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q122" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R122" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S122" t="n">
+      <c r="AW122" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX122" t="n">
         <v>7</v>
       </c>
-      <c r="T122" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="U122" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V122" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="W122" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X122" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y122" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z122" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AA122" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AB122" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC122" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD122" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="AE122" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF122" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AG122" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH122" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI122" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AJ122" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AK122" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AL122" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AM122" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AN122" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AO122" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AP122" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ122" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR122" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AS122" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AT122" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AU122" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV122" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW122" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX122" t="n">
-        <v>4</v>
-      </c>
       <c r="AY122" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AZ122" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC122" t="n">
         <v>7</v>
       </c>
-      <c r="BA122" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB122" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC122" t="n">
-        <v>11</v>
-      </c>
       <c r="BD122" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BE122" t="n">
         <v>9</v>
       </c>
       <c r="BF122" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BG122" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="BH122" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="BI122" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="BJ122" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="BK122" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="BL122" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="BM122" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="BN122" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="BO122" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="BP122" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="123">
@@ -27157,7 +27157,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="n">
-        <v>7859548</v>
+        <v>7859547</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -27177,35 +27177,35 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Central Córdoba SdE</t>
+          <t>Deportivo Táchira</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L123" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M123" t="n">
         <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>['15', '44', '53']</t>
+          <t>['66']</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -27214,160 +27214,160 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>2.25</v>
+        <v>1.3</v>
       </c>
       <c r="R123" t="n">
-        <v>2.25</v>
+        <v>3.75</v>
       </c>
       <c r="S123" t="n">
-        <v>5.5</v>
+        <v>19</v>
       </c>
       <c r="T123" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="U123" t="n">
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="V123" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="W123" t="n">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="X123" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="Y123" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="Z123" t="n">
-        <v>1.61</v>
+        <v>1.02</v>
       </c>
       <c r="AA123" t="n">
-        <v>3.78</v>
+        <v>12</v>
       </c>
       <c r="AB123" t="n">
-        <v>4.3</v>
+        <v>17</v>
       </c>
       <c r="AC123" t="n">
         <v>1.01</v>
       </c>
       <c r="AD123" t="n">
-        <v>10.2</v>
+        <v>11</v>
       </c>
       <c r="AE123" t="n">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="AF123" t="n">
-        <v>3.32</v>
+        <v>7.5</v>
       </c>
       <c r="AG123" t="n">
-        <v>1.88</v>
+        <v>1.25</v>
       </c>
       <c r="AH123" t="n">
-        <v>1.82</v>
+        <v>3.71</v>
       </c>
       <c r="AI123" t="n">
-        <v>1.95</v>
+        <v>2.63</v>
       </c>
       <c r="AJ123" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AK123" t="n">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="AL123" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="AM123" t="n">
-        <v>2.1</v>
+        <v>10</v>
       </c>
       <c r="AN123" t="n">
         <v>1.6</v>
       </c>
       <c r="AO123" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AQ123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>21</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN123" t="n">
         <v>1.83</v>
       </c>
-      <c r="AR123" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AS123" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AT123" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AU123" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV123" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW123" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX123" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY123" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ123" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA123" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB123" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC123" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD123" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BE123" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF123" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG123" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BH123" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BI123" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BJ123" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BK123" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BL123" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BM123" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BN123" t="n">
-        <v>1.73</v>
-      </c>
       <c r="BO123" t="n">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="BP123" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="124">
@@ -27507,10 +27507,10 @@
         <v>2</v>
       </c>
       <c r="AP124" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AR124" t="n">
         <v>1.57</v>
@@ -27943,10 +27943,10 @@
         <v>1.6</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR126" t="n">
         <v>1.75</v>
@@ -28379,10 +28379,10 @@
         <v>1.83</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AR128" t="n">
         <v>1.49</v>
@@ -28597,10 +28597,10 @@
         <v>2.17</v>
       </c>
       <c r="AP129" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR129" t="n">
         <v>1.57</v>
@@ -28815,10 +28815,10 @@
         <v>2.33</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ130" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AR130" t="n">
         <v>1.53</v>
@@ -30202,6 +30202,660 @@
       </c>
       <c r="BP136" t="n">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="n">
+        <v>7919114</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>45888.79166666666</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Vélez Sarsfield</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>2</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
+        <v>2</v>
+      </c>
+      <c r="L137" t="n">
+        <v>2</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" t="n">
+        <v>2</v>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>['7', '28']</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R137" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S137" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T137" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U137" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V137" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="W137" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X137" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="n">
+        <v>7919116</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>45888.89583333334</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>1</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>1</v>
+      </c>
+      <c r="L138" t="n">
+        <v>1</v>
+      </c>
+      <c r="M138" t="n">
+        <v>1</v>
+      </c>
+      <c r="N138" t="n">
+        <v>2</v>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>['3']</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>['70']</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R138" t="n">
+        <v>2</v>
+      </c>
+      <c r="S138" t="n">
+        <v>6</v>
+      </c>
+      <c r="T138" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U138" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V138" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="W138" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X138" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="n">
+        <v>7919115</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>45888.89583333334</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Racing Club</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Peñarol</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>1</v>
+      </c>
+      <c r="J139" t="n">
+        <v>1</v>
+      </c>
+      <c r="K139" t="n">
+        <v>2</v>
+      </c>
+      <c r="L139" t="n">
+        <v>3</v>
+      </c>
+      <c r="M139" t="n">
+        <v>1</v>
+      </c>
+      <c r="N139" t="n">
+        <v>4</v>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>['7', '83', '90+4']</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>['15']</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R139" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S139" t="n">
+        <v>6</v>
+      </c>
+      <c r="T139" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U139" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V139" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W139" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X139" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>26</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South America Copa Libertadores_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South America Copa Libertadores_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP139"/>
+  <dimension ref="A1:BP141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3530,7 +3530,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR14" t="n">
         <v>1.46</v>
@@ -5271,7 +5271,7 @@
         <v>2</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.5</v>
@@ -5928,7 +5928,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR25" t="n">
         <v>0.91</v>
@@ -6797,7 +6797,7 @@
         <v>2</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.5</v>
@@ -7454,7 +7454,7 @@
         <v>0.17</v>
       </c>
       <c r="AQ32" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AR32" t="n">
         <v>0</v>
@@ -7669,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ33" t="n">
         <v>1</v>
@@ -10288,7 +10288,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR45" t="n">
         <v>1.99</v>
@@ -10724,7 +10724,7 @@
         <v>0</v>
       </c>
       <c r="AQ47" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR47" t="n">
         <v>0</v>
@@ -11593,7 +11593,7 @@
         <v>3</v>
       </c>
       <c r="AP51" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AQ51" t="n">
         <v>1.67</v>
@@ -12683,7 +12683,7 @@
         <v>1</v>
       </c>
       <c r="AP56" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.83</v>
@@ -13122,7 +13122,7 @@
         <v>3</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR58" t="n">
         <v>0</v>
@@ -13773,7 +13773,7 @@
         <v>3</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ61" t="n">
         <v>1.38</v>
@@ -14648,7 +14648,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ65" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR65" t="n">
         <v>1.57</v>
@@ -15299,7 +15299,7 @@
         <v>0</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ68" t="n">
         <v>1.17</v>
@@ -16607,7 +16607,7 @@
         <v>1.5</v>
       </c>
       <c r="AP74" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AQ74" t="n">
         <v>2.14</v>
@@ -17697,7 +17697,7 @@
         <v>0</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ79" t="n">
         <v>0.67</v>
@@ -19444,7 +19444,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ87" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AR87" t="n">
         <v>0.99</v>
@@ -19659,7 +19659,7 @@
         <v>3</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ88" t="n">
         <v>3</v>
@@ -19880,7 +19880,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ89" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR89" t="n">
         <v>1.66</v>
@@ -20752,7 +20752,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR93" t="n">
         <v>1.65</v>
@@ -22060,7 +22060,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR99" t="n">
         <v>0.9399999999999999</v>
@@ -23150,7 +23150,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ104" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AR104" t="n">
         <v>1.46</v>
@@ -24022,7 +24022,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR108" t="n">
         <v>1.31</v>
@@ -24455,7 +24455,7 @@
         <v>2</v>
       </c>
       <c r="AP110" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ110" t="n">
         <v>1.57</v>
@@ -25545,7 +25545,7 @@
         <v>0.2</v>
       </c>
       <c r="AP115" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AQ115" t="n">
         <v>0.17</v>
@@ -26417,7 +26417,7 @@
         <v>1.67</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ119" t="n">
         <v>1.5</v>
@@ -26638,7 +26638,7 @@
         <v>1</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR120" t="n">
         <v>1.77</v>
@@ -27289,7 +27289,7 @@
         <v>0</v>
       </c>
       <c r="AP123" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ123" t="n">
         <v>0</v>
@@ -29033,10 +29033,10 @@
         <v>2</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ131" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AR131" t="n">
         <v>1.71</v>
@@ -29251,10 +29251,10 @@
         <v>1.83</v>
       </c>
       <c r="AP132" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR132" t="n">
         <v>1.44</v>
@@ -29687,10 +29687,10 @@
         <v>2.14</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ134" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AR134" t="n">
         <v>1.65</v>
@@ -30362,16 +30362,16 @@
         <v>3</v>
       </c>
       <c r="AW137" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AX137" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY137" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ137" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA137" t="n">
         <v>4</v>
@@ -30856,6 +30856,442 @@
       </c>
       <c r="BP139" t="n">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="n">
+        <v>7919117</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>45889.79166666666</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Estudiantes</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Cerro Porteño</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R140" t="n">
+        <v>2</v>
+      </c>
+      <c r="S140" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="T140" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U140" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V140" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="W140" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X140" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="n">
+        <v>7919118</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>45889.89583333334</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>1</v>
+      </c>
+      <c r="K141" t="n">
+        <v>1</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="n">
+        <v>2</v>
+      </c>
+      <c r="N141" t="n">
+        <v>2</v>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>['27', '88']</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R141" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S141" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T141" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U141" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V141" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W141" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X141" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South America Copa Libertadores_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South America Copa Libertadores_2025.xlsx
@@ -24912,16 +24912,16 @@
         <v>5</v>
       </c>
       <c r="AW112" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AX112" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY112" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ112" t="n">
         <v>10</v>
-      </c>
-      <c r="AY112" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ112" t="n">
-        <v>15</v>
       </c>
       <c r="BA112" t="n">
         <v>0</v>
@@ -25130,16 +25130,16 @@
         <v>4</v>
       </c>
       <c r="AW113" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX113" t="n">
         <v>9</v>
       </c>
-      <c r="AX113" t="n">
-        <v>8</v>
-      </c>
       <c r="AY113" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ113" t="n">
         <v>13</v>
-      </c>
-      <c r="AZ113" t="n">
-        <v>12</v>
       </c>
       <c r="BA113" t="n">
         <v>6</v>
@@ -25342,22 +25342,22 @@
         <v>2.96</v>
       </c>
       <c r="AU114" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV114" t="n">
         <v>1</v>
       </c>
       <c r="AW114" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AX114" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AY114" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AZ114" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="BA114" t="n">
         <v>4</v>
@@ -25560,22 +25560,22 @@
         <v>2.26</v>
       </c>
       <c r="AU115" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV115" t="n">
         <v>1</v>
       </c>
       <c r="AW115" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AX115" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AY115" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ115" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BA115" t="n">
         <v>4</v>
@@ -25778,19 +25778,19 @@
         <v>3.1</v>
       </c>
       <c r="AU116" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV116" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW116" t="n">
         <v>11</v>
-      </c>
-      <c r="AV116" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW116" t="n">
-        <v>12</v>
       </c>
       <c r="AX116" t="n">
         <v>3</v>
       </c>
       <c r="AY116" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AZ116" t="n">
         <v>5</v>
@@ -26002,16 +26002,16 @@
         <v>2</v>
       </c>
       <c r="AW117" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AX117" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ117" t="n">
         <v>7</v>
-      </c>
-      <c r="AY117" t="n">
-        <v>19</v>
-      </c>
-      <c r="AZ117" t="n">
-        <v>9</v>
       </c>
       <c r="BA117" t="n">
         <v>7</v>
@@ -27104,13 +27104,13 @@
         <v>11</v>
       </c>
       <c r="BA122" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB122" t="n">
         <v>2</v>
       </c>
       <c r="BC122" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD122" t="n">
         <v>1.2</v>
@@ -28385,13 +28385,13 @@
         <v>1.88</v>
       </c>
       <c r="AR128" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="AS128" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AT128" t="n">
-        <v>3.19</v>
+        <v>2.91</v>
       </c>
       <c r="AU128" t="n">
         <v>1</v>
@@ -28603,10 +28603,10 @@
         <v>2</v>
       </c>
       <c r="AR129" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AS129" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AT129" t="n">
         <v>3.32</v>
@@ -28821,13 +28821,13 @@
         <v>2</v>
       </c>
       <c r="AR130" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AS130" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AT130" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="AU130" t="n">
         <v>1</v>
@@ -29039,13 +29039,13 @@
         <v>2.11</v>
       </c>
       <c r="AR131" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AS131" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AT131" t="n">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="AU131" t="n">
         <v>5</v>
@@ -29257,13 +29257,13 @@
         <v>1.38</v>
       </c>
       <c r="AR132" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AS132" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AT132" t="n">
-        <v>2.81</v>
+        <v>2.93</v>
       </c>
       <c r="AU132" t="n">
         <v>4</v>
@@ -29475,13 +29475,13 @@
         <v>1.57</v>
       </c>
       <c r="AR133" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AS133" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AT133" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="AU133" t="n">
         <v>3</v>
@@ -29693,13 +29693,13 @@
         <v>2.11</v>
       </c>
       <c r="AR134" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AS134" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AT134" t="n">
-        <v>3.15</v>
+        <v>3.03</v>
       </c>
       <c r="AU134" t="n">
         <v>5</v>
@@ -29911,13 +29911,13 @@
         <v>1.86</v>
       </c>
       <c r="AR135" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AS135" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AT135" t="n">
-        <v>2.98</v>
+        <v>2.91</v>
       </c>
       <c r="AU135" t="n">
         <v>2</v>
@@ -30132,10 +30132,10 @@
         <v>1.22</v>
       </c>
       <c r="AS136" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AT136" t="n">
-        <v>3.03</v>
+        <v>3.17</v>
       </c>
       <c r="AU136" t="n">
         <v>2</v>
@@ -30347,13 +30347,13 @@
         <v>1.13</v>
       </c>
       <c r="AR137" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AS137" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AT137" t="n">
-        <v>3.07</v>
+        <v>2.84</v>
       </c>
       <c r="AU137" t="n">
         <v>3</v>
@@ -30565,13 +30565,13 @@
         <v>1.38</v>
       </c>
       <c r="AR138" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AS138" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AT138" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="AU138" t="n">
         <v>7</v>
@@ -30783,13 +30783,13 @@
         <v>1.75</v>
       </c>
       <c r="AR139" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AS139" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AT139" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="AU139" t="n">
         <v>7</v>
@@ -31001,13 +31001,13 @@
         <v>1.54</v>
       </c>
       <c r="AR140" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AS140" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AT140" t="n">
-        <v>3.15</v>
+        <v>3.03</v>
       </c>
       <c r="AU140" t="n">
         <v>2</v>
@@ -31219,13 +31219,13 @@
         <v>2.13</v>
       </c>
       <c r="AR141" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AS141" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="AT141" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="AU141" t="n">
         <v>1</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South America Copa Libertadores_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South America Copa Libertadores_2025.xlsx
@@ -30362,16 +30362,16 @@
         <v>3</v>
       </c>
       <c r="AW137" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AX137" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY137" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AZ137" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA137" t="n">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South America Copa Libertadores_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South America Copa Libertadores_2025.xlsx
@@ -30362,16 +30362,16 @@
         <v>3</v>
       </c>
       <c r="AW137" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AX137" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY137" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ137" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA137" t="n">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South America Copa Libertadores_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South America Copa Libertadores_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP141"/>
+  <dimension ref="A1:BP144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8326,7 +8326,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR36" t="n">
         <v>1.41</v>
@@ -9413,10 +9413,10 @@
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AR41" t="n">
         <v>0</v>
@@ -9634,7 +9634,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ42" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AR42" t="n">
         <v>0</v>
@@ -10070,7 +10070,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR44" t="n">
         <v>0</v>
@@ -10506,7 +10506,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ46" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AR46" t="n">
         <v>0</v>
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.67</v>
@@ -11157,7 +11157,7 @@
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AQ49" t="n">
         <v>0.17</v>
@@ -11811,7 +11811,7 @@
         <v>2</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.1</v>
@@ -12032,7 +12032,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR53" t="n">
         <v>1.19</v>
@@ -13119,7 +13119,7 @@
         <v>3</v>
       </c>
       <c r="AP58" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AQ58" t="n">
         <v>1.54</v>
@@ -13337,7 +13337,7 @@
         <v>0</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ59" t="n">
         <v>0</v>
@@ -14645,7 +14645,7 @@
         <v>1.5</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ65" t="n">
         <v>2.13</v>
@@ -15520,7 +15520,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR69" t="n">
         <v>1.1</v>
@@ -16171,7 +16171,7 @@
         <v>2</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ72" t="n">
         <v>2</v>
@@ -16392,7 +16392,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AR73" t="n">
         <v>1.4</v>
@@ -16610,7 +16610,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ74" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AR74" t="n">
         <v>1.42</v>
@@ -17264,7 +17264,7 @@
         <v>1</v>
       </c>
       <c r="AQ77" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AR77" t="n">
         <v>2.13</v>
@@ -18136,7 +18136,7 @@
         <v>0.17</v>
       </c>
       <c r="AQ81" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AR81" t="n">
         <v>0.76</v>
@@ -19008,7 +19008,7 @@
         <v>0</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR85" t="n">
         <v>0.92</v>
@@ -19662,7 +19662,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ88" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AR88" t="n">
         <v>1.8</v>
@@ -20534,7 +20534,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR92" t="n">
         <v>1.82</v>
@@ -20970,7 +20970,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AR94" t="n">
         <v>1.15</v>
@@ -21185,7 +21185,7 @@
         <v>1.33</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ95" t="n">
         <v>1.33</v>
@@ -23147,7 +23147,7 @@
         <v>2.25</v>
       </c>
       <c r="AP104" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AQ104" t="n">
         <v>2.11</v>
@@ -23368,7 +23368,7 @@
         <v>2</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR105" t="n">
         <v>1.41</v>
@@ -23583,7 +23583,7 @@
         <v>1.38</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ106" t="n">
         <v>1.1</v>
@@ -24237,7 +24237,7 @@
         <v>0.75</v>
       </c>
       <c r="AP109" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AQ109" t="n">
         <v>1</v>
@@ -24458,7 +24458,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR110" t="n">
         <v>1.3</v>
@@ -24673,7 +24673,7 @@
         <v>1.25</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.33</v>
@@ -25109,7 +25109,7 @@
         <v>1.36</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ113" t="n">
         <v>1.33</v>
@@ -25327,7 +25327,7 @@
         <v>2</v>
       </c>
       <c r="AP114" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.67</v>
@@ -25763,10 +25763,10 @@
         <v>1.4</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR116" t="n">
         <v>1.76</v>
@@ -26853,7 +26853,7 @@
         <v>0.8</v>
       </c>
       <c r="AP121" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AQ121" t="n">
         <v>0.67</v>
@@ -27071,7 +27071,7 @@
         <v>2.2</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ122" t="n">
         <v>1.83</v>
@@ -29469,10 +29469,10 @@
         <v>1.83</v>
       </c>
       <c r="AP133" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR133" t="n">
         <v>1.46</v>
@@ -29905,10 +29905,10 @@
         <v>2</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AR135" t="n">
         <v>1.03</v>
@@ -30123,10 +30123,10 @@
         <v>3</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ136" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AR136" t="n">
         <v>1.22</v>
@@ -31292,6 +31292,660 @@
       </c>
       <c r="BP141" t="n">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="n">
+        <v>8197174</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>45890.79166666666</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>LDU Quito</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>1</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>1</v>
+      </c>
+      <c r="L142" t="n">
+        <v>2</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" t="n">
+        <v>2</v>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>['7', '60']</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>3</v>
+      </c>
+      <c r="R142" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S142" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T142" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U142" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V142" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W142" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X142" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="n">
+        <v>7919119</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>45890.89583333334</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>1</v>
+      </c>
+      <c r="J143" t="n">
+        <v>1</v>
+      </c>
+      <c r="K143" t="n">
+        <v>2</v>
+      </c>
+      <c r="L143" t="n">
+        <v>1</v>
+      </c>
+      <c r="M143" t="n">
+        <v>1</v>
+      </c>
+      <c r="N143" t="n">
+        <v>2</v>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>['29']</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>['43']</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R143" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S143" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="T143" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U143" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V143" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W143" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X143" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="n">
+        <v>7919120</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>45890.89583333334</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Universitario</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R144" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S144" t="n">
+        <v>9</v>
+      </c>
+      <c r="T144" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U144" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V144" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W144" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X144" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AI144" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ144" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK144" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AL144" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AM144" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO144" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AP144" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AQ144" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AR144" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AS144" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT144" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AU144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV144" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW144" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX144" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY144" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ144" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA144" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB144" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC144" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD144" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BE144" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF144" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG144" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH144" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI144" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ144" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BK144" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BL144" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BM144" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BN144" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO144" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP144" t="n">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South America Copa Libertadores_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South America Copa Libertadores_2025.xlsx
@@ -30362,16 +30362,16 @@
         <v>3</v>
       </c>
       <c r="AW137" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AX137" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY137" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AZ137" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA137" t="n">
         <v>4</v>
@@ -30798,13 +30798,13 @@
         <v>6</v>
       </c>
       <c r="AW139" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX139" t="n">
         <v>10</v>
       </c>
       <c r="AY139" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ139" t="n">
         <v>16</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South America Copa Libertadores_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South America Copa Libertadores_2025.xlsx
@@ -31664,7 +31664,7 @@
         <v>2.94</v>
       </c>
       <c r="AU143" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV143" t="n">
         <v>8</v>
@@ -31676,7 +31676,7 @@
         <v>9</v>
       </c>
       <c r="AY143" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ143" t="n">
         <v>17</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South America Copa Libertadores_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South America Copa Libertadores_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP144"/>
+  <dimension ref="A1:BP145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7890,7 +7890,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ34" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR34" t="n">
         <v>0</v>
@@ -8759,7 +8759,7 @@
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.75</v>
@@ -12250,7 +12250,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AR54" t="n">
         <v>1.78</v>
@@ -13555,7 +13555,7 @@
         <v>1</v>
       </c>
       <c r="AP60" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ60" t="n">
         <v>1</v>
@@ -15302,7 +15302,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ68" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR68" t="n">
         <v>1.16</v>
@@ -15956,7 +15956,7 @@
         <v>1</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AR71" t="n">
         <v>1.09</v>
@@ -18354,7 +18354,7 @@
         <v>1</v>
       </c>
       <c r="AQ82" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR82" t="n">
         <v>1.6</v>
@@ -20313,7 +20313,7 @@
         <v>0.33</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ91" t="n">
         <v>0.83</v>
@@ -22493,7 +22493,7 @@
         <v>1.5</v>
       </c>
       <c r="AP101" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ101" t="n">
         <v>1</v>
@@ -23365,7 +23365,7 @@
         <v>0.5</v>
       </c>
       <c r="AP105" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ105" t="n">
         <v>0.83</v>
@@ -27510,7 +27510,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AR124" t="n">
         <v>1.57</v>
@@ -27943,7 +27943,7 @@
         <v>1.6</v>
       </c>
       <c r="AP126" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ126" t="n">
         <v>1.13</v>
@@ -28382,7 +28382,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AR128" t="n">
         <v>1.33</v>
@@ -28600,7 +28600,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ129" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR129" t="n">
         <v>1.58</v>
@@ -30341,7 +30341,7 @@
         <v>1.29</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.13</v>
@@ -30559,7 +30559,7 @@
         <v>2</v>
       </c>
       <c r="AP138" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ138" t="n">
         <v>1.75</v>
@@ -31946,6 +31946,224 @@
       </c>
       <c r="BP144" t="n">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="n">
+        <v>8215388</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>45916.79166666666</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Vélez Sarsfield</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Racing Club</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" t="n">
+        <v>1</v>
+      </c>
+      <c r="N145" t="n">
+        <v>1</v>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>['53']</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R145" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S145" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T145" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U145" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V145" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W145" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X145" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI145" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AJ145" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK145" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL145" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM145" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN145" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO145" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP145" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ145" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AR145" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS145" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AT145" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AU145" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV145" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW145" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX145" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY145" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ145" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA145" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC145" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD145" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BE145" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF145" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BG145" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH145" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BI145" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BJ145" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BK145" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BL145" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BM145" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BN145" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BO145" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP145" t="n">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South America Copa Libertadores_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South America Copa Libertadores_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP145"/>
+  <dimension ref="A1:BP146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9198,7 +9198,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR40" t="n">
         <v>0</v>
@@ -10070,7 +10070,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ44" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AR44" t="n">
         <v>0</v>
@@ -11811,7 +11811,7 @@
         <v>2</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.1</v>
@@ -13119,7 +13119,7 @@
         <v>3</v>
       </c>
       <c r="AP58" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ58" t="n">
         <v>1.54</v>
@@ -16174,7 +16174,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR72" t="n">
         <v>1.4</v>
@@ -17046,7 +17046,7 @@
         <v>1</v>
       </c>
       <c r="AQ76" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AR76" t="n">
         <v>2.13</v>
@@ -19662,7 +19662,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ88" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AR88" t="n">
         <v>1.8</v>
@@ -20752,7 +20752,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR93" t="n">
         <v>1.15</v>
@@ -24019,7 +24019,7 @@
         <v>0.75</v>
       </c>
       <c r="AP108" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ108" t="n">
         <v>1</v>
@@ -24673,7 +24673,7 @@
         <v>1.25</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.33</v>
@@ -25763,7 +25763,7 @@
         <v>1.4</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ116" t="n">
         <v>1.13</v>
@@ -26853,7 +26853,7 @@
         <v>0.8</v>
       </c>
       <c r="AP121" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ121" t="n">
         <v>0.67</v>
@@ -29908,7 +29908,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ135" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AR135" t="n">
         <v>1.22</v>
@@ -30126,7 +30126,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ136" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR136" t="n">
         <v>1.03</v>
@@ -31649,7 +31649,7 @@
         <v>1.43</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ143" t="n">
         <v>1.38</v>
@@ -31867,7 +31867,7 @@
         <v>1.14</v>
       </c>
       <c r="AP144" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ144" t="n">
         <v>1.13</v>
@@ -32164,6 +32164,224 @@
       </c>
       <c r="BP145" t="n">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="n">
+        <v>8230939</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>45917.89583333334</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>2</v>
+      </c>
+      <c r="K146" t="n">
+        <v>2</v>
+      </c>
+      <c r="L146" t="n">
+        <v>1</v>
+      </c>
+      <c r="M146" t="n">
+        <v>2</v>
+      </c>
+      <c r="N146" t="n">
+        <v>3</v>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>['6', '41']</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="R146" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="S146" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="T146" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U146" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="V146" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="W146" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X146" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="AE146" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AF146" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AG146" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH146" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI146" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ146" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AK146" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AL146" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AM146" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN146" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO146" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AP146" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ146" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AR146" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS146" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AT146" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AU146" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV146" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW146" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX146" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY146" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ146" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA146" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB146" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC146" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD146" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BE146" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF146" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG146" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BH146" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BI146" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BJ146" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BK146" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BL146" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BM146" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BN146" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BO146" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP146" t="n">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South America Copa Libertadores_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South America Copa Libertadores_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP146"/>
+  <dimension ref="A1:BP148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7454,7 +7454,7 @@
         <v>0.17</v>
       </c>
       <c r="AQ32" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AR32" t="n">
         <v>0</v>
@@ -9416,7 +9416,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ41" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR41" t="n">
         <v>0</v>
@@ -10288,7 +10288,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AR45" t="n">
         <v>0</v>
@@ -10724,7 +10724,7 @@
         <v>0</v>
       </c>
       <c r="AQ47" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR47" t="n">
         <v>0</v>
@@ -11593,7 +11593,7 @@
         <v>3</v>
       </c>
       <c r="AP51" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ51" t="n">
         <v>1.67</v>
@@ -12901,7 +12901,7 @@
         <v>1</v>
       </c>
       <c r="AP57" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ57" t="n">
         <v>1.83</v>
@@ -13337,7 +13337,7 @@
         <v>0</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ59" t="n">
         <v>0</v>
@@ -14209,7 +14209,7 @@
         <v>1.57</v>
       </c>
       <c r="AP63" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ63" t="n">
         <v>1.33</v>
@@ -14645,10 +14645,10 @@
         <v>1.5</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ65" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR65" t="n">
         <v>1.57</v>
@@ -16389,7 +16389,7 @@
         <v>1.5</v>
       </c>
       <c r="AP73" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.88</v>
@@ -16610,7 +16610,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ74" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR74" t="n">
         <v>1.07</v>
@@ -18136,7 +18136,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ81" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR81" t="n">
         <v>1.46</v>
@@ -19008,7 +19008,7 @@
         <v>0</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AR85" t="n">
         <v>0.92</v>
@@ -19444,7 +19444,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ87" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AR87" t="n">
         <v>0.99</v>
@@ -19880,7 +19880,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ89" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR89" t="n">
         <v>1.66</v>
@@ -22932,7 +22932,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ103" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AR103" t="n">
         <v>1.46</v>
@@ -23147,7 +23147,7 @@
         <v>1.75</v>
       </c>
       <c r="AP104" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ104" t="n">
         <v>1.38</v>
@@ -24455,10 +24455,10 @@
         <v>2</v>
       </c>
       <c r="AP110" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AR110" t="n">
         <v>1.3</v>
@@ -24891,7 +24891,7 @@
         <v>0.8</v>
       </c>
       <c r="AP112" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ112" t="n">
         <v>0.67</v>
@@ -25545,7 +25545,7 @@
         <v>0.2</v>
       </c>
       <c r="AP115" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ115" t="n">
         <v>0.17</v>
@@ -27071,7 +27071,7 @@
         <v>0</v>
       </c>
       <c r="AP122" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ122" t="n">
         <v>0</v>
@@ -27289,7 +27289,7 @@
         <v>2.2</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ123" t="n">
         <v>1.83</v>
@@ -28818,7 +28818,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ130" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR130" t="n">
         <v>1.48</v>
@@ -29036,7 +29036,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ131" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AR131" t="n">
         <v>1.61</v>
@@ -29251,7 +29251,7 @@
         <v>1.83</v>
       </c>
       <c r="AP132" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ132" t="n">
         <v>1.38</v>
@@ -29472,7 +29472,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AR133" t="n">
         <v>1.46</v>
@@ -29690,7 +29690,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ134" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AR134" t="n">
         <v>1.56</v>
@@ -30777,7 +30777,7 @@
         <v>1.43</v>
       </c>
       <c r="AP139" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.38</v>
@@ -30995,7 +30995,7 @@
         <v>1.58</v>
       </c>
       <c r="AP140" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ140" t="n">
         <v>1.54</v>
@@ -31216,7 +31216,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ141" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR141" t="n">
         <v>1.26</v>
@@ -31431,7 +31431,7 @@
         <v>2.14</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ142" t="n">
         <v>1.88</v>
@@ -32382,6 +32382,442 @@
       </c>
       <c r="BP146" t="n">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="n">
+        <v>8230940</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>45918.79166666666</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>LDU Quito</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>1</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n">
+        <v>1</v>
+      </c>
+      <c r="L147" t="n">
+        <v>2</v>
+      </c>
+      <c r="M147" t="n">
+        <v>0</v>
+      </c>
+      <c r="N147" t="n">
+        <v>2</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>['15', '78']</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R147" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="S147" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T147" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U147" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="V147" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W147" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X147" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI147" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AK147" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL147" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM147" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN147" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AQ147" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AR147" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AS147" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AT147" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU147" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV147" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX147" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY147" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ147" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA147" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB147" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC147" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD147" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BE147" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF147" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BG147" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH147" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI147" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BJ147" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BK147" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BL147" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BM147" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BN147" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO147" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP147" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="n">
+        <v>8228154</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>45918.89583333334</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Estudiantes</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>2</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
+        <v>2</v>
+      </c>
+      <c r="L148" t="n">
+        <v>2</v>
+      </c>
+      <c r="M148" t="n">
+        <v>1</v>
+      </c>
+      <c r="N148" t="n">
+        <v>3</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>['1', '9']</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>['90+1']</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R148" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="S148" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="T148" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U148" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="V148" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="W148" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X148" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF148" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH148" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI148" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AJ148" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AK148" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AL148" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AM148" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AN148" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AO148" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AP148" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AQ148" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AR148" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS148" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AT148" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU148" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV148" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW148" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX148" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY148" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ148" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA148" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB148" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC148" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD148" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BE148" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF148" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BG148" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH148" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BI148" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BJ148" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BK148" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BL148" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BM148" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BN148" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BO148" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BP148" t="n">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South America Copa Libertadores_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South America Copa Libertadores_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP148"/>
+  <dimension ref="A1:BP149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7890,7 +7890,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ34" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AR34" t="n">
         <v>0</v>
@@ -8759,7 +8759,7 @@
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.75</v>
@@ -12250,7 +12250,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR54" t="n">
         <v>1.78</v>
@@ -13555,7 +13555,7 @@
         <v>1</v>
       </c>
       <c r="AP60" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ60" t="n">
         <v>1</v>
@@ -15302,7 +15302,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ68" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AR68" t="n">
         <v>1.16</v>
@@ -15956,7 +15956,7 @@
         <v>1</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR71" t="n">
         <v>1.09</v>
@@ -18354,7 +18354,7 @@
         <v>1</v>
       </c>
       <c r="AQ82" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AR82" t="n">
         <v>1.6</v>
@@ -20313,7 +20313,7 @@
         <v>0.33</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ91" t="n">
         <v>0.83</v>
@@ -22493,7 +22493,7 @@
         <v>1.5</v>
       </c>
       <c r="AP101" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ101" t="n">
         <v>1</v>
@@ -23365,7 +23365,7 @@
         <v>0.5</v>
       </c>
       <c r="AP105" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ105" t="n">
         <v>0.83</v>
@@ -27510,7 +27510,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR124" t="n">
         <v>1.57</v>
@@ -27943,7 +27943,7 @@
         <v>1.6</v>
       </c>
       <c r="AP126" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ126" t="n">
         <v>1.13</v>
@@ -28382,7 +28382,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR128" t="n">
         <v>1.33</v>
@@ -28600,7 +28600,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ129" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AR129" t="n">
         <v>1.58</v>
@@ -30341,7 +30341,7 @@
         <v>1.29</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.13</v>
@@ -30559,7 +30559,7 @@
         <v>2</v>
       </c>
       <c r="AP138" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ138" t="n">
         <v>1.75</v>
@@ -32085,10 +32085,10 @@
         <v>2</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ145" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AR145" t="n">
         <v>1.52</v>
@@ -32818,6 +32818,224 @@
       </c>
       <c r="BP148" t="n">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="n">
+        <v>8215389</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>45923.79166666666</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Racing Club</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Vélez Sarsfield</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" t="n">
+        <v>0</v>
+      </c>
+      <c r="N149" t="n">
+        <v>1</v>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>['82']</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="R149" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S149" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T149" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U149" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V149" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W149" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X149" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI149" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ149" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK149" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL149" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AM149" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN149" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ149" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR149" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS149" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AT149" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AU149" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW149" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX149" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY149" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ149" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA149" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB149" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC149" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD149" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BE149" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF149" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG149" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BH149" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI149" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BJ149" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BK149" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BL149" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BM149" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BN149" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BO149" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BP149" t="n">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>
